--- a/qa-suites/master-qa-summary-report.xlsx
+++ b/qa-suites/master-qa-summary-report.xlsx
@@ -38,7 +38,7 @@
     <t>Report Date</t>
   </si>
   <si>
-    <t>24/7/2026, 6:38:01 pm</t>
+    <t>24/7/2026, 7:24:50 pm</t>
   </si>
   <si>
     <t>Total QA Metrics Summary (750 Test Cases)</t>
@@ -7359,7 +7359,7 @@
         <v>46</v>
       </c>
       <c r="K2" s="7">
-        <v>384</v>
+        <v>55</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>47</v>
@@ -7397,7 +7397,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="9">
-        <v>220</v>
+        <v>291</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>47</v>
@@ -7435,7 +7435,7 @@
         <v>57</v>
       </c>
       <c r="K4" s="7">
-        <v>217</v>
+        <v>30</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>47</v>
@@ -7473,7 +7473,7 @@
         <v>46</v>
       </c>
       <c r="K5" s="9">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>47</v>
@@ -7511,7 +7511,7 @@
         <v>52</v>
       </c>
       <c r="K6" s="7">
-        <v>32</v>
+        <v>341</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>47</v>
@@ -7549,7 +7549,7 @@
         <v>57</v>
       </c>
       <c r="K7" s="9">
-        <v>442</v>
+        <v>152</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>47</v>
@@ -7587,7 +7587,7 @@
         <v>46</v>
       </c>
       <c r="K8" s="7">
-        <v>144</v>
+        <v>400</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>47</v>
@@ -7625,7 +7625,7 @@
         <v>52</v>
       </c>
       <c r="K9" s="9">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>47</v>
@@ -7663,7 +7663,7 @@
         <v>57</v>
       </c>
       <c r="K10" s="7">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>47</v>
@@ -7701,7 +7701,7 @@
         <v>46</v>
       </c>
       <c r="K11" s="9">
-        <v>231</v>
+        <v>56</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>47</v>
@@ -7739,7 +7739,7 @@
         <v>52</v>
       </c>
       <c r="K12" s="7">
-        <v>276</v>
+        <v>111</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>47</v>
@@ -7777,7 +7777,7 @@
         <v>57</v>
       </c>
       <c r="K13" s="9">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>47</v>
@@ -7815,7 +7815,7 @@
         <v>46</v>
       </c>
       <c r="K14" s="7">
-        <v>49</v>
+        <v>313</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>47</v>
@@ -7853,7 +7853,7 @@
         <v>52</v>
       </c>
       <c r="K15" s="9">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>47</v>
@@ -7891,7 +7891,7 @@
         <v>57</v>
       </c>
       <c r="K16" s="7">
-        <v>469</v>
+        <v>277</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>47</v>
@@ -7929,7 +7929,7 @@
         <v>46</v>
       </c>
       <c r="K17" s="9">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>47</v>
@@ -7967,7 +7967,7 @@
         <v>52</v>
       </c>
       <c r="K18" s="7">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>47</v>
@@ -8005,7 +8005,7 @@
         <v>57</v>
       </c>
       <c r="K19" s="9">
-        <v>65</v>
+        <v>332</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>47</v>
@@ -8043,7 +8043,7 @@
         <v>46</v>
       </c>
       <c r="K20" s="7">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>47</v>
@@ -8081,7 +8081,7 @@
         <v>52</v>
       </c>
       <c r="K21" s="9">
-        <v>411</v>
+        <v>293</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>47</v>
@@ -8119,7 +8119,7 @@
         <v>57</v>
       </c>
       <c r="K22" s="7">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>47</v>
@@ -8157,7 +8157,7 @@
         <v>46</v>
       </c>
       <c r="K23" s="9">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>47</v>
@@ -8195,7 +8195,7 @@
         <v>52</v>
       </c>
       <c r="K24" s="7">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>47</v>
@@ -8233,7 +8233,7 @@
         <v>57</v>
       </c>
       <c r="K25" s="9">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>47</v>
@@ -8271,7 +8271,7 @@
         <v>46</v>
       </c>
       <c r="K26" s="7">
-        <v>87</v>
+        <v>388</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>47</v>
@@ -8309,7 +8309,7 @@
         <v>52</v>
       </c>
       <c r="K27" s="9">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>47</v>
@@ -8347,7 +8347,7 @@
         <v>57</v>
       </c>
       <c r="K28" s="7">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>47</v>
@@ -8385,7 +8385,7 @@
         <v>46</v>
       </c>
       <c r="K29" s="9">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>47</v>
@@ -8423,7 +8423,7 @@
         <v>52</v>
       </c>
       <c r="K30" s="7">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>47</v>
@@ -8461,7 +8461,7 @@
         <v>57</v>
       </c>
       <c r="K31" s="9">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>47</v>
@@ -8499,7 +8499,7 @@
         <v>46</v>
       </c>
       <c r="K32" s="7">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>47</v>
@@ -8537,7 +8537,7 @@
         <v>52</v>
       </c>
       <c r="K33" s="9">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>47</v>
@@ -8575,7 +8575,7 @@
         <v>57</v>
       </c>
       <c r="K34" s="7">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>47</v>
@@ -8613,7 +8613,7 @@
         <v>46</v>
       </c>
       <c r="K35" s="9">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>47</v>
@@ -8651,7 +8651,7 @@
         <v>52</v>
       </c>
       <c r="K36" s="7">
-        <v>178</v>
+        <v>455</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>47</v>
@@ -8689,7 +8689,7 @@
         <v>57</v>
       </c>
       <c r="K37" s="9">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>47</v>
@@ -8727,7 +8727,7 @@
         <v>46</v>
       </c>
       <c r="K38" s="7">
-        <v>403</v>
+        <v>235</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>162</v>
@@ -8765,7 +8765,7 @@
         <v>52</v>
       </c>
       <c r="K39" s="9">
-        <v>466</v>
+        <v>121</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>47</v>
@@ -8803,7 +8803,7 @@
         <v>57</v>
       </c>
       <c r="K40" s="7">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>47</v>
@@ -8841,7 +8841,7 @@
         <v>46</v>
       </c>
       <c r="K41" s="9">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>47</v>
@@ -8879,7 +8879,7 @@
         <v>52</v>
       </c>
       <c r="K42" s="7">
-        <v>193</v>
+        <v>393</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>47</v>
@@ -8917,7 +8917,7 @@
         <v>57</v>
       </c>
       <c r="K43" s="9">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>47</v>
@@ -8955,7 +8955,7 @@
         <v>46</v>
       </c>
       <c r="K44" s="7">
-        <v>390</v>
+        <v>185</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>47</v>
@@ -8993,7 +8993,7 @@
         <v>52</v>
       </c>
       <c r="K45" s="9">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>47</v>
@@ -9031,7 +9031,7 @@
         <v>57</v>
       </c>
       <c r="K46" s="7">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>47</v>
@@ -9069,7 +9069,7 @@
         <v>46</v>
       </c>
       <c r="K47" s="9">
-        <v>87</v>
+        <v>387</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>47</v>
@@ -9107,7 +9107,7 @@
         <v>52</v>
       </c>
       <c r="K48" s="7">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>47</v>
@@ -9145,7 +9145,7 @@
         <v>57</v>
       </c>
       <c r="K49" s="9">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>47</v>
@@ -9183,7 +9183,7 @@
         <v>46</v>
       </c>
       <c r="K50" s="7">
-        <v>231</v>
+        <v>450</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>47</v>
@@ -9221,7 +9221,7 @@
         <v>52</v>
       </c>
       <c r="K51" s="9">
-        <v>32</v>
+        <v>299</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>47</v>
@@ -9259,7 +9259,7 @@
         <v>57</v>
       </c>
       <c r="K52" s="7">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>47</v>
@@ -9297,7 +9297,7 @@
         <v>46</v>
       </c>
       <c r="K53" s="9">
-        <v>29</v>
+        <v>409</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>47</v>
@@ -9335,7 +9335,7 @@
         <v>52</v>
       </c>
       <c r="K54" s="7">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>47</v>
@@ -9373,7 +9373,7 @@
         <v>57</v>
       </c>
       <c r="K55" s="9">
-        <v>423</v>
+        <v>76</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>47</v>
@@ -9411,7 +9411,7 @@
         <v>46</v>
       </c>
       <c r="K56" s="7">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L56" s="8" t="s">
         <v>47</v>
@@ -9449,7 +9449,7 @@
         <v>52</v>
       </c>
       <c r="K57" s="9">
-        <v>395</v>
+        <v>27</v>
       </c>
       <c r="L57" s="8" t="s">
         <v>47</v>
@@ -9487,7 +9487,7 @@
         <v>57</v>
       </c>
       <c r="K58" s="7">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>47</v>
@@ -9525,7 +9525,7 @@
         <v>46</v>
       </c>
       <c r="K59" s="9">
-        <v>387</v>
+        <v>185</v>
       </c>
       <c r="L59" s="8" t="s">
         <v>47</v>
@@ -9563,7 +9563,7 @@
         <v>52</v>
       </c>
       <c r="K60" s="7">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>47</v>
@@ -9601,7 +9601,7 @@
         <v>57</v>
       </c>
       <c r="K61" s="9">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>47</v>
@@ -9639,7 +9639,7 @@
         <v>46</v>
       </c>
       <c r="K62" s="7">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="L62" s="8" t="s">
         <v>47</v>
@@ -9677,7 +9677,7 @@
         <v>52</v>
       </c>
       <c r="K63" s="9">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>47</v>
@@ -9715,7 +9715,7 @@
         <v>57</v>
       </c>
       <c r="K64" s="7">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>47</v>
@@ -9753,7 +9753,7 @@
         <v>46</v>
       </c>
       <c r="K65" s="9">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="L65" s="8" t="s">
         <v>47</v>
@@ -9791,7 +9791,7 @@
         <v>52</v>
       </c>
       <c r="K66" s="7">
-        <v>295</v>
+        <v>388</v>
       </c>
       <c r="L66" s="8" t="s">
         <v>47</v>
@@ -9829,7 +9829,7 @@
         <v>57</v>
       </c>
       <c r="K67" s="9">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>47</v>
@@ -9867,7 +9867,7 @@
         <v>46</v>
       </c>
       <c r="K68" s="7">
-        <v>225</v>
+        <v>447</v>
       </c>
       <c r="L68" s="11" t="s">
         <v>253</v>
@@ -9905,7 +9905,7 @@
         <v>52</v>
       </c>
       <c r="K69" s="9">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>47</v>
@@ -9943,7 +9943,7 @@
         <v>57</v>
       </c>
       <c r="K70" s="7">
-        <v>464</v>
+        <v>110</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>47</v>
@@ -9981,7 +9981,7 @@
         <v>46</v>
       </c>
       <c r="K71" s="9">
-        <v>397</v>
+        <v>458</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>47</v>
@@ -10019,7 +10019,7 @@
         <v>52</v>
       </c>
       <c r="K72" s="7">
-        <v>331</v>
+        <v>200</v>
       </c>
       <c r="L72" s="8" t="s">
         <v>47</v>
@@ -10057,7 +10057,7 @@
         <v>57</v>
       </c>
       <c r="K73" s="9">
-        <v>400</v>
+        <v>141</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>47</v>
@@ -10095,7 +10095,7 @@
         <v>46</v>
       </c>
       <c r="K74" s="7">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="L74" s="8" t="s">
         <v>47</v>
@@ -10133,7 +10133,7 @@
         <v>52</v>
       </c>
       <c r="K75" s="9">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="L75" s="10" t="s">
         <v>162</v>
@@ -10171,7 +10171,7 @@
         <v>57</v>
       </c>
       <c r="K76" s="7">
-        <v>373</v>
+        <v>465</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>47</v>
@@ -10209,7 +10209,7 @@
         <v>46</v>
       </c>
       <c r="K77" s="9">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>47</v>
@@ -10247,7 +10247,7 @@
         <v>52</v>
       </c>
       <c r="K78" s="7">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>47</v>
@@ -10285,7 +10285,7 @@
         <v>57</v>
       </c>
       <c r="K79" s="9">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="L79" s="8" t="s">
         <v>47</v>
@@ -10323,7 +10323,7 @@
         <v>46</v>
       </c>
       <c r="K80" s="7">
-        <v>435</v>
+        <v>342</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>47</v>
@@ -10361,7 +10361,7 @@
         <v>52</v>
       </c>
       <c r="K81" s="9">
-        <v>428</v>
+        <v>308</v>
       </c>
       <c r="L81" s="8" t="s">
         <v>47</v>
@@ -10399,7 +10399,7 @@
         <v>57</v>
       </c>
       <c r="K82" s="7">
-        <v>22</v>
+        <v>257</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>47</v>
@@ -10437,7 +10437,7 @@
         <v>46</v>
       </c>
       <c r="K83" s="9">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>47</v>
@@ -10475,7 +10475,7 @@
         <v>52</v>
       </c>
       <c r="K84" s="7">
-        <v>271</v>
+        <v>401</v>
       </c>
       <c r="L84" s="8" t="s">
         <v>47</v>
@@ -10513,7 +10513,7 @@
         <v>57</v>
       </c>
       <c r="K85" s="9">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>47</v>
@@ -10551,7 +10551,7 @@
         <v>46</v>
       </c>
       <c r="K86" s="7">
-        <v>409</v>
+        <v>100</v>
       </c>
       <c r="L86" s="8" t="s">
         <v>47</v>
@@ -10589,7 +10589,7 @@
         <v>52</v>
       </c>
       <c r="K87" s="9">
-        <v>116</v>
+        <v>282</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>47</v>
@@ -10627,7 +10627,7 @@
         <v>57</v>
       </c>
       <c r="K88" s="7">
-        <v>468</v>
+        <v>129</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>47</v>
@@ -10665,7 +10665,7 @@
         <v>46</v>
       </c>
       <c r="K89" s="9">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="L89" s="8" t="s">
         <v>47</v>
@@ -10703,7 +10703,7 @@
         <v>52</v>
       </c>
       <c r="K90" s="7">
-        <v>266</v>
+        <v>438</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>47</v>
@@ -10741,7 +10741,7 @@
         <v>57</v>
       </c>
       <c r="K91" s="9">
-        <v>461</v>
+        <v>56</v>
       </c>
       <c r="L91" s="8" t="s">
         <v>47</v>
@@ -10779,7 +10779,7 @@
         <v>46</v>
       </c>
       <c r="K92" s="7">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="L92" s="8" t="s">
         <v>47</v>
@@ -10817,7 +10817,7 @@
         <v>52</v>
       </c>
       <c r="K93" s="9">
-        <v>236</v>
+        <v>402</v>
       </c>
       <c r="L93" s="8" t="s">
         <v>47</v>
@@ -10855,7 +10855,7 @@
         <v>57</v>
       </c>
       <c r="K94" s="7">
-        <v>293</v>
+        <v>38</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>47</v>
@@ -10893,7 +10893,7 @@
         <v>46</v>
       </c>
       <c r="K95" s="9">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="L95" s="8" t="s">
         <v>47</v>
@@ -10931,7 +10931,7 @@
         <v>52</v>
       </c>
       <c r="K96" s="7">
-        <v>125</v>
+        <v>317</v>
       </c>
       <c r="L96" s="8" t="s">
         <v>47</v>
@@ -10969,7 +10969,7 @@
         <v>57</v>
       </c>
       <c r="K97" s="9">
-        <v>422</v>
+        <v>210</v>
       </c>
       <c r="L97" s="8" t="s">
         <v>47</v>
@@ -11007,7 +11007,7 @@
         <v>46</v>
       </c>
       <c r="K98" s="7">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="L98" s="8" t="s">
         <v>47</v>
@@ -11045,7 +11045,7 @@
         <v>52</v>
       </c>
       <c r="K99" s="9">
-        <v>304</v>
+        <v>462</v>
       </c>
       <c r="L99" s="8" t="s">
         <v>47</v>
@@ -11083,7 +11083,7 @@
         <v>57</v>
       </c>
       <c r="K100" s="7">
-        <v>386</v>
+        <v>176</v>
       </c>
       <c r="L100" s="8" t="s">
         <v>47</v>
@@ -11121,7 +11121,7 @@
         <v>46</v>
       </c>
       <c r="K101" s="9">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="L101" s="8" t="s">
         <v>47</v>
@@ -11159,7 +11159,7 @@
         <v>52</v>
       </c>
       <c r="K102" s="7">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="L102" s="8" t="s">
         <v>47</v>
@@ -11197,7 +11197,7 @@
         <v>57</v>
       </c>
       <c r="K103" s="9">
-        <v>382</v>
+        <v>457</v>
       </c>
       <c r="L103" s="8" t="s">
         <v>47</v>
@@ -11235,7 +11235,7 @@
         <v>46</v>
       </c>
       <c r="K104" s="7">
-        <v>298</v>
+        <v>67</v>
       </c>
       <c r="L104" s="8" t="s">
         <v>47</v>
@@ -11273,7 +11273,7 @@
         <v>52</v>
       </c>
       <c r="K105" s="9">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="L105" s="8" t="s">
         <v>47</v>
@@ -11311,7 +11311,7 @@
         <v>57</v>
       </c>
       <c r="K106" s="7">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="L106" s="8" t="s">
         <v>47</v>
@@ -11349,7 +11349,7 @@
         <v>46</v>
       </c>
       <c r="K107" s="9">
-        <v>85</v>
+        <v>444</v>
       </c>
       <c r="L107" s="8" t="s">
         <v>47</v>
@@ -11387,7 +11387,7 @@
         <v>52</v>
       </c>
       <c r="K108" s="7">
-        <v>319</v>
+        <v>101</v>
       </c>
       <c r="L108" s="8" t="s">
         <v>47</v>
@@ -11425,7 +11425,7 @@
         <v>57</v>
       </c>
       <c r="K109" s="9">
-        <v>253</v>
+        <v>408</v>
       </c>
       <c r="L109" s="8" t="s">
         <v>47</v>
@@ -11463,7 +11463,7 @@
         <v>46</v>
       </c>
       <c r="K110" s="7">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="L110" s="8" t="s">
         <v>47</v>
@@ -11501,7 +11501,7 @@
         <v>52</v>
       </c>
       <c r="K111" s="9">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="L111" s="8" t="s">
         <v>47</v>
@@ -11539,7 +11539,7 @@
         <v>57</v>
       </c>
       <c r="K112" s="7">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="L112" s="10" t="s">
         <v>162</v>
@@ -11577,7 +11577,7 @@
         <v>46</v>
       </c>
       <c r="K113" s="9">
-        <v>228</v>
+        <v>317</v>
       </c>
       <c r="L113" s="8" t="s">
         <v>47</v>
@@ -11615,7 +11615,7 @@
         <v>52</v>
       </c>
       <c r="K114" s="7">
-        <v>267</v>
+        <v>148</v>
       </c>
       <c r="L114" s="8" t="s">
         <v>47</v>
@@ -11653,7 +11653,7 @@
         <v>57</v>
       </c>
       <c r="K115" s="9">
-        <v>312</v>
+        <v>56</v>
       </c>
       <c r="L115" s="8" t="s">
         <v>47</v>
@@ -11691,7 +11691,7 @@
         <v>46</v>
       </c>
       <c r="K116" s="7">
-        <v>383</v>
+        <v>264</v>
       </c>
       <c r="L116" s="8" t="s">
         <v>47</v>
@@ -11729,7 +11729,7 @@
         <v>52</v>
       </c>
       <c r="K117" s="9">
-        <v>161</v>
+        <v>422</v>
       </c>
       <c r="L117" s="8" t="s">
         <v>47</v>
@@ -11767,7 +11767,7 @@
         <v>57</v>
       </c>
       <c r="K118" s="7">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="L118" s="8" t="s">
         <v>47</v>
@@ -11805,7 +11805,7 @@
         <v>46</v>
       </c>
       <c r="K119" s="9">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="L119" s="8" t="s">
         <v>47</v>
@@ -11843,7 +11843,7 @@
         <v>52</v>
       </c>
       <c r="K120" s="7">
-        <v>271</v>
+        <v>28</v>
       </c>
       <c r="L120" s="8" t="s">
         <v>47</v>
@@ -11881,7 +11881,7 @@
         <v>57</v>
       </c>
       <c r="K121" s="9">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="L121" s="8" t="s">
         <v>47</v>
@@ -11919,7 +11919,7 @@
         <v>46</v>
       </c>
       <c r="K122" s="7">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="L122" s="8" t="s">
         <v>47</v>
@@ -11957,7 +11957,7 @@
         <v>52</v>
       </c>
       <c r="K123" s="9">
-        <v>299</v>
+        <v>220</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>47</v>
@@ -11995,7 +11995,7 @@
         <v>57</v>
       </c>
       <c r="K124" s="7">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>47</v>
@@ -12033,7 +12033,7 @@
         <v>46</v>
       </c>
       <c r="K125" s="9">
-        <v>317</v>
+        <v>34</v>
       </c>
       <c r="L125" s="8" t="s">
         <v>47</v>
@@ -12071,7 +12071,7 @@
         <v>52</v>
       </c>
       <c r="K126" s="7">
-        <v>226</v>
+        <v>382</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>47</v>
@@ -12109,7 +12109,7 @@
         <v>57</v>
       </c>
       <c r="K127" s="9">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="L127" s="8" t="s">
         <v>47</v>
@@ -12147,7 +12147,7 @@
         <v>46</v>
       </c>
       <c r="K128" s="7">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>47</v>
@@ -12185,7 +12185,7 @@
         <v>52</v>
       </c>
       <c r="K129" s="9">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>47</v>
@@ -12223,7 +12223,7 @@
         <v>57</v>
       </c>
       <c r="K130" s="7">
-        <v>384</v>
+        <v>46</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>47</v>
@@ -12261,7 +12261,7 @@
         <v>46</v>
       </c>
       <c r="K131" s="9">
-        <v>407</v>
+        <v>172</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>47</v>
@@ -12299,7 +12299,7 @@
         <v>52</v>
       </c>
       <c r="K132" s="7">
-        <v>350</v>
+        <v>132</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>47</v>
@@ -12337,7 +12337,7 @@
         <v>57</v>
       </c>
       <c r="K133" s="9">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="L133" s="8" t="s">
         <v>47</v>
@@ -12375,7 +12375,7 @@
         <v>46</v>
       </c>
       <c r="K134" s="7">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="L134" s="8" t="s">
         <v>47</v>
@@ -12413,7 +12413,7 @@
         <v>52</v>
       </c>
       <c r="K135" s="9">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="L135" s="11" t="s">
         <v>253</v>
@@ -12451,7 +12451,7 @@
         <v>57</v>
       </c>
       <c r="K136" s="7">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="L136" s="8" t="s">
         <v>47</v>
@@ -12489,7 +12489,7 @@
         <v>46</v>
       </c>
       <c r="K137" s="9">
-        <v>54</v>
+        <v>179</v>
       </c>
       <c r="L137" s="8" t="s">
         <v>47</v>
@@ -12527,7 +12527,7 @@
         <v>52</v>
       </c>
       <c r="K138" s="7">
-        <v>291</v>
+        <v>455</v>
       </c>
       <c r="L138" s="8" t="s">
         <v>47</v>
@@ -12565,7 +12565,7 @@
         <v>57</v>
       </c>
       <c r="K139" s="9">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="L139" s="8" t="s">
         <v>47</v>
@@ -12603,7 +12603,7 @@
         <v>46</v>
       </c>
       <c r="K140" s="7">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L140" s="8" t="s">
         <v>47</v>
@@ -12641,7 +12641,7 @@
         <v>52</v>
       </c>
       <c r="K141" s="9">
-        <v>455</v>
+        <v>181</v>
       </c>
       <c r="L141" s="8" t="s">
         <v>47</v>
@@ -12679,7 +12679,7 @@
         <v>57</v>
       </c>
       <c r="K142" s="7">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>47</v>
@@ -12717,7 +12717,7 @@
         <v>46</v>
       </c>
       <c r="K143" s="9">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="L143" s="8" t="s">
         <v>47</v>
@@ -12755,7 +12755,7 @@
         <v>52</v>
       </c>
       <c r="K144" s="7">
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>47</v>
@@ -12793,7 +12793,7 @@
         <v>57</v>
       </c>
       <c r="K145" s="9">
-        <v>53</v>
+        <v>334</v>
       </c>
       <c r="L145" s="8" t="s">
         <v>47</v>
@@ -12831,7 +12831,7 @@
         <v>46</v>
       </c>
       <c r="K146" s="7">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="L146" s="8" t="s">
         <v>47</v>
@@ -12869,7 +12869,7 @@
         <v>52</v>
       </c>
       <c r="K147" s="9">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="L147" s="8" t="s">
         <v>47</v>
@@ -12907,7 +12907,7 @@
         <v>57</v>
       </c>
       <c r="K148" s="7">
-        <v>440</v>
+        <v>332</v>
       </c>
       <c r="L148" s="8" t="s">
         <v>47</v>
@@ -12945,7 +12945,7 @@
         <v>46</v>
       </c>
       <c r="K149" s="9">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="L149" s="10" t="s">
         <v>162</v>
@@ -12983,7 +12983,7 @@
         <v>52</v>
       </c>
       <c r="K150" s="7">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="L150" s="8" t="s">
         <v>47</v>
@@ -13021,7 +13021,7 @@
         <v>57</v>
       </c>
       <c r="K151" s="9">
-        <v>118</v>
+        <v>469</v>
       </c>
       <c r="L151" s="8" t="s">
         <v>47</v>
@@ -13059,7 +13059,7 @@
         <v>46</v>
       </c>
       <c r="K152" s="7">
-        <v>449</v>
+        <v>219</v>
       </c>
       <c r="L152" s="8" t="s">
         <v>47</v>
@@ -13097,7 +13097,7 @@
         <v>52</v>
       </c>
       <c r="K153" s="9">
-        <v>447</v>
+        <v>101</v>
       </c>
       <c r="L153" s="8" t="s">
         <v>47</v>
@@ -13135,7 +13135,7 @@
         <v>57</v>
       </c>
       <c r="K154" s="7">
-        <v>251</v>
+        <v>66</v>
       </c>
       <c r="L154" s="8" t="s">
         <v>47</v>
@@ -13173,7 +13173,7 @@
         <v>46</v>
       </c>
       <c r="K155" s="9">
-        <v>294</v>
+        <v>33</v>
       </c>
       <c r="L155" s="8" t="s">
         <v>47</v>
@@ -13211,7 +13211,7 @@
         <v>52</v>
       </c>
       <c r="K156" s="7">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="L156" s="8" t="s">
         <v>47</v>
@@ -13249,7 +13249,7 @@
         <v>57</v>
       </c>
       <c r="K157" s="9">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="L157" s="8" t="s">
         <v>47</v>
@@ -13287,7 +13287,7 @@
         <v>46</v>
       </c>
       <c r="K158" s="7">
-        <v>124</v>
+        <v>283</v>
       </c>
       <c r="L158" s="8" t="s">
         <v>47</v>
@@ -13325,7 +13325,7 @@
         <v>52</v>
       </c>
       <c r="K159" s="9">
-        <v>284</v>
+        <v>94</v>
       </c>
       <c r="L159" s="8" t="s">
         <v>47</v>
@@ -13363,7 +13363,7 @@
         <v>57</v>
       </c>
       <c r="K160" s="7">
-        <v>441</v>
+        <v>68</v>
       </c>
       <c r="L160" s="8" t="s">
         <v>47</v>
@@ -13401,7 +13401,7 @@
         <v>46</v>
       </c>
       <c r="K161" s="9">
-        <v>168</v>
+        <v>324</v>
       </c>
       <c r="L161" s="8" t="s">
         <v>47</v>
@@ -13439,7 +13439,7 @@
         <v>52</v>
       </c>
       <c r="K162" s="7">
-        <v>198</v>
+        <v>40</v>
       </c>
       <c r="L162" s="8" t="s">
         <v>47</v>
@@ -13477,7 +13477,7 @@
         <v>57</v>
       </c>
       <c r="K163" s="9">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="L163" s="8" t="s">
         <v>47</v>
@@ -13515,7 +13515,7 @@
         <v>46</v>
       </c>
       <c r="K164" s="7">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="L164" s="8" t="s">
         <v>47</v>
@@ -13553,7 +13553,7 @@
         <v>52</v>
       </c>
       <c r="K165" s="9">
-        <v>306</v>
+        <v>48</v>
       </c>
       <c r="L165" s="8" t="s">
         <v>47</v>
@@ -13591,7 +13591,7 @@
         <v>57</v>
       </c>
       <c r="K166" s="7">
-        <v>348</v>
+        <v>213</v>
       </c>
       <c r="L166" s="8" t="s">
         <v>47</v>
@@ -13629,7 +13629,7 @@
         <v>46</v>
       </c>
       <c r="K167" s="9">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="L167" s="8" t="s">
         <v>47</v>
@@ -13667,7 +13667,7 @@
         <v>52</v>
       </c>
       <c r="K168" s="7">
-        <v>88</v>
+        <v>406</v>
       </c>
       <c r="L168" s="8" t="s">
         <v>47</v>
@@ -13705,7 +13705,7 @@
         <v>57</v>
       </c>
       <c r="K169" s="9">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="L169" s="8" t="s">
         <v>47</v>
@@ -13743,7 +13743,7 @@
         <v>46</v>
       </c>
       <c r="K170" s="7">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="L170" s="8" t="s">
         <v>47</v>
@@ -13781,7 +13781,7 @@
         <v>52</v>
       </c>
       <c r="K171" s="9">
-        <v>36</v>
+        <v>447</v>
       </c>
       <c r="L171" s="8" t="s">
         <v>47</v>
@@ -13819,7 +13819,7 @@
         <v>57</v>
       </c>
       <c r="K172" s="7">
-        <v>398</v>
+        <v>57</v>
       </c>
       <c r="L172" s="8" t="s">
         <v>47</v>
@@ -13857,7 +13857,7 @@
         <v>46</v>
       </c>
       <c r="K173" s="9">
-        <v>439</v>
+        <v>392</v>
       </c>
       <c r="L173" s="8" t="s">
         <v>47</v>
@@ -13895,7 +13895,7 @@
         <v>52</v>
       </c>
       <c r="K174" s="7">
-        <v>124</v>
+        <v>414</v>
       </c>
       <c r="L174" s="8" t="s">
         <v>47</v>
@@ -13933,7 +13933,7 @@
         <v>57</v>
       </c>
       <c r="K175" s="9">
-        <v>197</v>
+        <v>313</v>
       </c>
       <c r="L175" s="8" t="s">
         <v>47</v>
@@ -13971,7 +13971,7 @@
         <v>46</v>
       </c>
       <c r="K176" s="7">
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="L176" s="8" t="s">
         <v>47</v>
@@ -14009,7 +14009,7 @@
         <v>52</v>
       </c>
       <c r="K177" s="9">
-        <v>227</v>
+        <v>385</v>
       </c>
       <c r="L177" s="8" t="s">
         <v>47</v>
@@ -14047,7 +14047,7 @@
         <v>57</v>
       </c>
       <c r="K178" s="7">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="L178" s="8" t="s">
         <v>47</v>
@@ -14085,7 +14085,7 @@
         <v>46</v>
       </c>
       <c r="K179" s="9">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="L179" s="8" t="s">
         <v>47</v>
@@ -14123,7 +14123,7 @@
         <v>52</v>
       </c>
       <c r="K180" s="7">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="L180" s="8" t="s">
         <v>47</v>
@@ -14161,7 +14161,7 @@
         <v>57</v>
       </c>
       <c r="K181" s="9">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="L181" s="8" t="s">
         <v>47</v>
@@ -14199,7 +14199,7 @@
         <v>46</v>
       </c>
       <c r="K182" s="7">
-        <v>94</v>
+        <v>462</v>
       </c>
       <c r="L182" s="8" t="s">
         <v>47</v>
@@ -14237,7 +14237,7 @@
         <v>52</v>
       </c>
       <c r="K183" s="9">
-        <v>399</v>
+        <v>30</v>
       </c>
       <c r="L183" s="8" t="s">
         <v>47</v>
@@ -14275,7 +14275,7 @@
         <v>57</v>
       </c>
       <c r="K184" s="7">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="L184" s="8" t="s">
         <v>47</v>
@@ -14313,7 +14313,7 @@
         <v>46</v>
       </c>
       <c r="K185" s="9">
-        <v>451</v>
+        <v>63</v>
       </c>
       <c r="L185" s="8" t="s">
         <v>47</v>
@@ -14351,7 +14351,7 @@
         <v>52</v>
       </c>
       <c r="K186" s="7">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="L186" s="10" t="s">
         <v>162</v>
@@ -14389,7 +14389,7 @@
         <v>57</v>
       </c>
       <c r="K187" s="9">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="L187" s="8" t="s">
         <v>47</v>
@@ -14427,7 +14427,7 @@
         <v>46</v>
       </c>
       <c r="K188" s="7">
-        <v>281</v>
+        <v>321</v>
       </c>
       <c r="L188" s="8" t="s">
         <v>47</v>
@@ -14465,7 +14465,7 @@
         <v>52</v>
       </c>
       <c r="K189" s="9">
-        <v>43</v>
+        <v>363</v>
       </c>
       <c r="L189" s="8" t="s">
         <v>47</v>
@@ -14503,7 +14503,7 @@
         <v>57</v>
       </c>
       <c r="K190" s="7">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="L190" s="8" t="s">
         <v>47</v>
@@ -14541,7 +14541,7 @@
         <v>46</v>
       </c>
       <c r="K191" s="9">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="L191" s="8" t="s">
         <v>47</v>
@@ -14579,7 +14579,7 @@
         <v>52</v>
       </c>
       <c r="K192" s="7">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="L192" s="8" t="s">
         <v>47</v>
@@ -14617,7 +14617,7 @@
         <v>57</v>
       </c>
       <c r="K193" s="9">
-        <v>445</v>
+        <v>149</v>
       </c>
       <c r="L193" s="8" t="s">
         <v>47</v>
@@ -14655,7 +14655,7 @@
         <v>46</v>
       </c>
       <c r="K194" s="7">
-        <v>336</v>
+        <v>215</v>
       </c>
       <c r="L194" s="8" t="s">
         <v>47</v>
@@ -14693,7 +14693,7 @@
         <v>52</v>
       </c>
       <c r="K195" s="9">
-        <v>353</v>
+        <v>287</v>
       </c>
       <c r="L195" s="8" t="s">
         <v>47</v>
@@ -14731,7 +14731,7 @@
         <v>57</v>
       </c>
       <c r="K196" s="7">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c r="L196" s="8" t="s">
         <v>47</v>
@@ -14769,7 +14769,7 @@
         <v>46</v>
       </c>
       <c r="K197" s="9">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="L197" s="8" t="s">
         <v>47</v>
@@ -14807,7 +14807,7 @@
         <v>52</v>
       </c>
       <c r="K198" s="7">
-        <v>465</v>
+        <v>122</v>
       </c>
       <c r="L198" s="8" t="s">
         <v>47</v>
@@ -14845,7 +14845,7 @@
         <v>57</v>
       </c>
       <c r="K199" s="9">
-        <v>321</v>
+        <v>114</v>
       </c>
       <c r="L199" s="8" t="s">
         <v>47</v>
@@ -14883,7 +14883,7 @@
         <v>46</v>
       </c>
       <c r="K200" s="7">
-        <v>124</v>
+        <v>350</v>
       </c>
       <c r="L200" s="8" t="s">
         <v>47</v>
@@ -14921,7 +14921,7 @@
         <v>52</v>
       </c>
       <c r="K201" s="9">
-        <v>449</v>
+        <v>112</v>
       </c>
       <c r="L201" s="8" t="s">
         <v>47</v>
@@ -14959,7 +14959,7 @@
         <v>57</v>
       </c>
       <c r="K202" s="7">
-        <v>349</v>
+        <v>204</v>
       </c>
       <c r="L202" s="11" t="s">
         <v>253</v>
@@ -14997,7 +14997,7 @@
         <v>46</v>
       </c>
       <c r="K203" s="9">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="L203" s="8" t="s">
         <v>47</v>
@@ -15035,7 +15035,7 @@
         <v>52</v>
       </c>
       <c r="K204" s="7">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="L204" s="8" t="s">
         <v>47</v>
@@ -15073,7 +15073,7 @@
         <v>57</v>
       </c>
       <c r="K205" s="9">
-        <v>54</v>
+        <v>372</v>
       </c>
       <c r="L205" s="8" t="s">
         <v>47</v>
@@ -15111,7 +15111,7 @@
         <v>46</v>
       </c>
       <c r="K206" s="7">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="L206" s="8" t="s">
         <v>47</v>
@@ -15149,7 +15149,7 @@
         <v>52</v>
       </c>
       <c r="K207" s="9">
-        <v>282</v>
+        <v>360</v>
       </c>
       <c r="L207" s="8" t="s">
         <v>47</v>
@@ -15187,7 +15187,7 @@
         <v>57</v>
       </c>
       <c r="K208" s="7">
-        <v>411</v>
+        <v>329</v>
       </c>
       <c r="L208" s="8" t="s">
         <v>47</v>
@@ -15225,7 +15225,7 @@
         <v>46</v>
       </c>
       <c r="K209" s="9">
-        <v>60</v>
+        <v>367</v>
       </c>
       <c r="L209" s="8" t="s">
         <v>47</v>
@@ -15263,7 +15263,7 @@
         <v>52</v>
       </c>
       <c r="K210" s="7">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="L210" s="8" t="s">
         <v>47</v>
@@ -15301,7 +15301,7 @@
         <v>57</v>
       </c>
       <c r="K211" s="9">
-        <v>215</v>
+        <v>110</v>
       </c>
       <c r="L211" s="8" t="s">
         <v>47</v>
@@ -15339,7 +15339,7 @@
         <v>46</v>
       </c>
       <c r="K212" s="7">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="L212" s="8" t="s">
         <v>47</v>
@@ -15377,7 +15377,7 @@
         <v>52</v>
       </c>
       <c r="K213" s="9">
-        <v>433</v>
+        <v>23</v>
       </c>
       <c r="L213" s="8" t="s">
         <v>47</v>
@@ -15415,7 +15415,7 @@
         <v>57</v>
       </c>
       <c r="K214" s="7">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="L214" s="8" t="s">
         <v>47</v>
@@ -15453,7 +15453,7 @@
         <v>46</v>
       </c>
       <c r="K215" s="9">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="L215" s="8" t="s">
         <v>47</v>
@@ -15491,7 +15491,7 @@
         <v>52</v>
       </c>
       <c r="K216" s="7">
-        <v>374</v>
+        <v>450</v>
       </c>
       <c r="L216" s="8" t="s">
         <v>47</v>
@@ -15529,7 +15529,7 @@
         <v>57</v>
       </c>
       <c r="K217" s="9">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="L217" s="8" t="s">
         <v>47</v>
@@ -15567,7 +15567,7 @@
         <v>46</v>
       </c>
       <c r="K218" s="7">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="L218" s="8" t="s">
         <v>47</v>
@@ -15605,7 +15605,7 @@
         <v>52</v>
       </c>
       <c r="K219" s="9">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="L219" s="8" t="s">
         <v>47</v>
@@ -15643,7 +15643,7 @@
         <v>57</v>
       </c>
       <c r="K220" s="7">
-        <v>398</v>
+        <v>253</v>
       </c>
       <c r="L220" s="8" t="s">
         <v>47</v>
@@ -15681,7 +15681,7 @@
         <v>46</v>
       </c>
       <c r="K221" s="9">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="L221" s="8" t="s">
         <v>47</v>
@@ -15719,7 +15719,7 @@
         <v>52</v>
       </c>
       <c r="K222" s="7">
-        <v>393</v>
+        <v>143</v>
       </c>
       <c r="L222" s="8" t="s">
         <v>47</v>
@@ -15757,7 +15757,7 @@
         <v>57</v>
       </c>
       <c r="K223" s="9">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="L223" s="10" t="s">
         <v>162</v>
@@ -15795,7 +15795,7 @@
         <v>46</v>
       </c>
       <c r="K224" s="7">
-        <v>217</v>
+        <v>382</v>
       </c>
       <c r="L224" s="8" t="s">
         <v>47</v>
@@ -15833,7 +15833,7 @@
         <v>52</v>
       </c>
       <c r="K225" s="9">
-        <v>406</v>
+        <v>28</v>
       </c>
       <c r="L225" s="8" t="s">
         <v>47</v>
@@ -15871,7 +15871,7 @@
         <v>57</v>
       </c>
       <c r="K226" s="7">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="L226" s="8" t="s">
         <v>47</v>
@@ -15909,7 +15909,7 @@
         <v>46</v>
       </c>
       <c r="K227" s="9">
-        <v>314</v>
+        <v>193</v>
       </c>
       <c r="L227" s="8" t="s">
         <v>47</v>
@@ -15947,7 +15947,7 @@
         <v>52</v>
       </c>
       <c r="K228" s="7">
-        <v>309</v>
+        <v>104</v>
       </c>
       <c r="L228" s="8" t="s">
         <v>47</v>
@@ -15985,7 +15985,7 @@
         <v>57</v>
       </c>
       <c r="K229" s="9">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L229" s="8" t="s">
         <v>47</v>
@@ -16023,7 +16023,7 @@
         <v>46</v>
       </c>
       <c r="K230" s="7">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="L230" s="8" t="s">
         <v>47</v>
@@ -16061,7 +16061,7 @@
         <v>52</v>
       </c>
       <c r="K231" s="9">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="L231" s="8" t="s">
         <v>47</v>
@@ -16099,7 +16099,7 @@
         <v>57</v>
       </c>
       <c r="K232" s="7">
-        <v>155</v>
+        <v>303</v>
       </c>
       <c r="L232" s="8" t="s">
         <v>47</v>
@@ -16137,7 +16137,7 @@
         <v>46</v>
       </c>
       <c r="K233" s="9">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="L233" s="8" t="s">
         <v>47</v>
@@ -16175,7 +16175,7 @@
         <v>52</v>
       </c>
       <c r="K234" s="7">
-        <v>355</v>
+        <v>419</v>
       </c>
       <c r="L234" s="8" t="s">
         <v>47</v>
@@ -16213,7 +16213,7 @@
         <v>57</v>
       </c>
       <c r="K235" s="9">
-        <v>455</v>
+        <v>76</v>
       </c>
       <c r="L235" s="8" t="s">
         <v>47</v>
@@ -16251,7 +16251,7 @@
         <v>46</v>
       </c>
       <c r="K236" s="7">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="L236" s="8" t="s">
         <v>47</v>
@@ -16289,7 +16289,7 @@
         <v>52</v>
       </c>
       <c r="K237" s="9">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="L237" s="8" t="s">
         <v>47</v>
@@ -16327,7 +16327,7 @@
         <v>57</v>
       </c>
       <c r="K238" s="7">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="L238" s="8" t="s">
         <v>47</v>
@@ -16365,7 +16365,7 @@
         <v>46</v>
       </c>
       <c r="K239" s="9">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="L239" s="8" t="s">
         <v>47</v>
@@ -16403,7 +16403,7 @@
         <v>52</v>
       </c>
       <c r="K240" s="7">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="L240" s="8" t="s">
         <v>47</v>
@@ -16441,7 +16441,7 @@
         <v>57</v>
       </c>
       <c r="K241" s="9">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="L241" s="8" t="s">
         <v>47</v>
@@ -16479,7 +16479,7 @@
         <v>46</v>
       </c>
       <c r="K242" s="7">
-        <v>333</v>
+        <v>119</v>
       </c>
       <c r="L242" s="8" t="s">
         <v>47</v>
@@ -16517,7 +16517,7 @@
         <v>52</v>
       </c>
       <c r="K243" s="9">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="L243" s="8" t="s">
         <v>47</v>
@@ -16555,7 +16555,7 @@
         <v>57</v>
       </c>
       <c r="K244" s="7">
-        <v>294</v>
+        <v>123</v>
       </c>
       <c r="L244" s="8" t="s">
         <v>47</v>
@@ -16593,7 +16593,7 @@
         <v>46</v>
       </c>
       <c r="K245" s="9">
-        <v>244</v>
+        <v>400</v>
       </c>
       <c r="L245" s="8" t="s">
         <v>47</v>
@@ -16631,7 +16631,7 @@
         <v>52</v>
       </c>
       <c r="K246" s="7">
-        <v>100</v>
+        <v>361</v>
       </c>
       <c r="L246" s="8" t="s">
         <v>47</v>
@@ -16669,7 +16669,7 @@
         <v>57</v>
       </c>
       <c r="K247" s="9">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="L247" s="8" t="s">
         <v>47</v>
@@ -16707,7 +16707,7 @@
         <v>46</v>
       </c>
       <c r="K248" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L248" s="8" t="s">
         <v>47</v>
@@ -16745,7 +16745,7 @@
         <v>52</v>
       </c>
       <c r="K249" s="9">
-        <v>61</v>
+        <v>346</v>
       </c>
       <c r="L249" s="8" t="s">
         <v>47</v>
@@ -16783,7 +16783,7 @@
         <v>57</v>
       </c>
       <c r="K250" s="7">
-        <v>141</v>
+        <v>368</v>
       </c>
       <c r="L250" s="8" t="s">
         <v>47</v>
@@ -16821,7 +16821,7 @@
         <v>46</v>
       </c>
       <c r="K251" s="9">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="L251" s="8" t="s">
         <v>47</v>
@@ -16859,7 +16859,7 @@
         <v>52</v>
       </c>
       <c r="K252" s="7">
-        <v>226</v>
+        <v>394</v>
       </c>
       <c r="L252" s="8" t="s">
         <v>47</v>
@@ -16897,7 +16897,7 @@
         <v>57</v>
       </c>
       <c r="K253" s="9">
-        <v>358</v>
+        <v>293</v>
       </c>
       <c r="L253" s="8" t="s">
         <v>47</v>
@@ -16935,7 +16935,7 @@
         <v>46</v>
       </c>
       <c r="K254" s="7">
-        <v>80</v>
+        <v>447</v>
       </c>
       <c r="L254" s="8" t="s">
         <v>47</v>
@@ -16973,7 +16973,7 @@
         <v>52</v>
       </c>
       <c r="K255" s="9">
-        <v>293</v>
+        <v>214</v>
       </c>
       <c r="L255" s="8" t="s">
         <v>47</v>
@@ -17011,7 +17011,7 @@
         <v>57</v>
       </c>
       <c r="K256" s="7">
-        <v>378</v>
+        <v>165</v>
       </c>
       <c r="L256" s="8" t="s">
         <v>47</v>
@@ -17049,7 +17049,7 @@
         <v>46</v>
       </c>
       <c r="K257" s="9">
-        <v>297</v>
+        <v>103</v>
       </c>
       <c r="L257" s="8" t="s">
         <v>47</v>
@@ -17087,7 +17087,7 @@
         <v>52</v>
       </c>
       <c r="K258" s="7">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="L258" s="8" t="s">
         <v>47</v>
@@ -17125,7 +17125,7 @@
         <v>57</v>
       </c>
       <c r="K259" s="9">
-        <v>371</v>
+        <v>449</v>
       </c>
       <c r="L259" s="8" t="s">
         <v>47</v>
@@ -17163,7 +17163,7 @@
         <v>46</v>
       </c>
       <c r="K260" s="7">
-        <v>233</v>
+        <v>36</v>
       </c>
       <c r="L260" s="10" t="s">
         <v>162</v>
@@ -17201,7 +17201,7 @@
         <v>52</v>
       </c>
       <c r="K261" s="9">
-        <v>311</v>
+        <v>457</v>
       </c>
       <c r="L261" s="8" t="s">
         <v>47</v>
@@ -17239,7 +17239,7 @@
         <v>57</v>
       </c>
       <c r="K262" s="7">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="L262" s="8" t="s">
         <v>47</v>
@@ -17277,7 +17277,7 @@
         <v>46</v>
       </c>
       <c r="K263" s="9">
-        <v>301</v>
+        <v>142</v>
       </c>
       <c r="L263" s="8" t="s">
         <v>47</v>
@@ -17315,7 +17315,7 @@
         <v>52</v>
       </c>
       <c r="K264" s="7">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="L264" s="8" t="s">
         <v>47</v>
@@ -17353,7 +17353,7 @@
         <v>57</v>
       </c>
       <c r="K265" s="9">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="L265" s="8" t="s">
         <v>47</v>
@@ -17391,7 +17391,7 @@
         <v>46</v>
       </c>
       <c r="K266" s="7">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="L266" s="8" t="s">
         <v>47</v>
@@ -17429,7 +17429,7 @@
         <v>52</v>
       </c>
       <c r="K267" s="9">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="L267" s="8" t="s">
         <v>47</v>
@@ -17467,7 +17467,7 @@
         <v>57</v>
       </c>
       <c r="K268" s="7">
-        <v>375</v>
+        <v>301</v>
       </c>
       <c r="L268" s="8" t="s">
         <v>47</v>
@@ -17505,7 +17505,7 @@
         <v>46</v>
       </c>
       <c r="K269" s="9">
-        <v>146</v>
+        <v>263</v>
       </c>
       <c r="L269" s="11" t="s">
         <v>253</v>
@@ -17543,7 +17543,7 @@
         <v>52</v>
       </c>
       <c r="K270" s="7">
-        <v>294</v>
+        <v>40</v>
       </c>
       <c r="L270" s="8" t="s">
         <v>47</v>
@@ -17581,7 +17581,7 @@
         <v>57</v>
       </c>
       <c r="K271" s="9">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="L271" s="8" t="s">
         <v>47</v>
@@ -17619,7 +17619,7 @@
         <v>46</v>
       </c>
       <c r="K272" s="7">
-        <v>177</v>
+        <v>280</v>
       </c>
       <c r="L272" s="8" t="s">
         <v>47</v>
@@ -17657,7 +17657,7 @@
         <v>52</v>
       </c>
       <c r="K273" s="9">
-        <v>411</v>
+        <v>460</v>
       </c>
       <c r="L273" s="8" t="s">
         <v>47</v>
@@ -17695,7 +17695,7 @@
         <v>57</v>
       </c>
       <c r="K274" s="7">
-        <v>399</v>
+        <v>278</v>
       </c>
       <c r="L274" s="8" t="s">
         <v>47</v>
@@ -17733,7 +17733,7 @@
         <v>46</v>
       </c>
       <c r="K275" s="9">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="L275" s="8" t="s">
         <v>47</v>
@@ -17771,7 +17771,7 @@
         <v>52</v>
       </c>
       <c r="K276" s="7">
-        <v>57</v>
+        <v>223</v>
       </c>
       <c r="L276" s="8" t="s">
         <v>47</v>
@@ -17809,7 +17809,7 @@
         <v>57</v>
       </c>
       <c r="K277" s="9">
-        <v>32</v>
+        <v>310</v>
       </c>
       <c r="L277" s="8" t="s">
         <v>47</v>
@@ -17847,7 +17847,7 @@
         <v>46</v>
       </c>
       <c r="K278" s="7">
-        <v>202</v>
+        <v>368</v>
       </c>
       <c r="L278" s="8" t="s">
         <v>47</v>
@@ -17885,7 +17885,7 @@
         <v>52</v>
       </c>
       <c r="K279" s="9">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="L279" s="8" t="s">
         <v>47</v>
@@ -17923,7 +17923,7 @@
         <v>57</v>
       </c>
       <c r="K280" s="7">
-        <v>295</v>
+        <v>208</v>
       </c>
       <c r="L280" s="8" t="s">
         <v>47</v>
@@ -17961,7 +17961,7 @@
         <v>46</v>
       </c>
       <c r="K281" s="9">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="L281" s="8" t="s">
         <v>47</v>
@@ -17999,7 +17999,7 @@
         <v>52</v>
       </c>
       <c r="K282" s="7">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="L282" s="8" t="s">
         <v>47</v>
@@ -18037,7 +18037,7 @@
         <v>57</v>
       </c>
       <c r="K283" s="9">
-        <v>391</v>
+        <v>245</v>
       </c>
       <c r="L283" s="8" t="s">
         <v>47</v>
@@ -18075,7 +18075,7 @@
         <v>46</v>
       </c>
       <c r="K284" s="7">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="L284" s="8" t="s">
         <v>47</v>
@@ -18113,7 +18113,7 @@
         <v>52</v>
       </c>
       <c r="K285" s="9">
-        <v>356</v>
+        <v>39</v>
       </c>
       <c r="L285" s="8" t="s">
         <v>47</v>
@@ -18151,7 +18151,7 @@
         <v>57</v>
       </c>
       <c r="K286" s="7">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="L286" s="8" t="s">
         <v>47</v>
@@ -18189,7 +18189,7 @@
         <v>46</v>
       </c>
       <c r="K287" s="9">
-        <v>263</v>
+        <v>456</v>
       </c>
       <c r="L287" s="8" t="s">
         <v>47</v>
@@ -18227,7 +18227,7 @@
         <v>52</v>
       </c>
       <c r="K288" s="7">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="L288" s="8" t="s">
         <v>47</v>
@@ -18265,7 +18265,7 @@
         <v>57</v>
       </c>
       <c r="K289" s="9">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="L289" s="8" t="s">
         <v>47</v>
@@ -18303,7 +18303,7 @@
         <v>46</v>
       </c>
       <c r="K290" s="7">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="L290" s="8" t="s">
         <v>47</v>
@@ -18341,7 +18341,7 @@
         <v>52</v>
       </c>
       <c r="K291" s="9">
-        <v>199</v>
+        <v>318</v>
       </c>
       <c r="L291" s="8" t="s">
         <v>47</v>
@@ -18379,7 +18379,7 @@
         <v>57</v>
       </c>
       <c r="K292" s="7">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="L292" s="8" t="s">
         <v>47</v>
@@ -18417,7 +18417,7 @@
         <v>46</v>
       </c>
       <c r="K293" s="9">
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="L293" s="8" t="s">
         <v>47</v>
@@ -18455,7 +18455,7 @@
         <v>52</v>
       </c>
       <c r="K294" s="7">
-        <v>158</v>
+        <v>454</v>
       </c>
       <c r="L294" s="8" t="s">
         <v>47</v>
@@ -18493,7 +18493,7 @@
         <v>57</v>
       </c>
       <c r="K295" s="9">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="L295" s="8" t="s">
         <v>47</v>
@@ -18531,7 +18531,7 @@
         <v>46</v>
       </c>
       <c r="K296" s="7">
-        <v>393</v>
+        <v>27</v>
       </c>
       <c r="L296" s="8" t="s">
         <v>47</v>
@@ -18569,7 +18569,7 @@
         <v>52</v>
       </c>
       <c r="K297" s="9">
-        <v>156</v>
+        <v>373</v>
       </c>
       <c r="L297" s="10" t="s">
         <v>162</v>
@@ -18607,7 +18607,7 @@
         <v>57</v>
       </c>
       <c r="K298" s="7">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="L298" s="8" t="s">
         <v>47</v>
@@ -18645,7 +18645,7 @@
         <v>46</v>
       </c>
       <c r="K299" s="9">
-        <v>346</v>
+        <v>163</v>
       </c>
       <c r="L299" s="8" t="s">
         <v>47</v>
@@ -18683,7 +18683,7 @@
         <v>52</v>
       </c>
       <c r="K300" s="7">
-        <v>413</v>
+        <v>215</v>
       </c>
       <c r="L300" s="8" t="s">
         <v>47</v>
@@ -18721,7 +18721,7 @@
         <v>57</v>
       </c>
       <c r="K301" s="9">
-        <v>401</v>
+        <v>37</v>
       </c>
       <c r="L301" s="8" t="s">
         <v>47</v>
@@ -18759,7 +18759,7 @@
         <v>46</v>
       </c>
       <c r="K302" s="7">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="L302" s="8" t="s">
         <v>47</v>
@@ -18797,7 +18797,7 @@
         <v>52</v>
       </c>
       <c r="K303" s="9">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="L303" s="8" t="s">
         <v>47</v>
@@ -18835,7 +18835,7 @@
         <v>57</v>
       </c>
       <c r="K304" s="7">
-        <v>177</v>
+        <v>462</v>
       </c>
       <c r="L304" s="8" t="s">
         <v>47</v>
@@ -18873,7 +18873,7 @@
         <v>46</v>
       </c>
       <c r="K305" s="9">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="L305" s="8" t="s">
         <v>47</v>
@@ -18911,7 +18911,7 @@
         <v>52</v>
       </c>
       <c r="K306" s="7">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="L306" s="8" t="s">
         <v>47</v>
@@ -18949,7 +18949,7 @@
         <v>57</v>
       </c>
       <c r="K307" s="9">
-        <v>60</v>
+        <v>461</v>
       </c>
       <c r="L307" s="8" t="s">
         <v>47</v>
@@ -18987,7 +18987,7 @@
         <v>46</v>
       </c>
       <c r="K308" s="7">
-        <v>420</v>
+        <v>298</v>
       </c>
       <c r="L308" s="8" t="s">
         <v>47</v>
@@ -19025,7 +19025,7 @@
         <v>52</v>
       </c>
       <c r="K309" s="9">
-        <v>332</v>
+        <v>266</v>
       </c>
       <c r="L309" s="8" t="s">
         <v>47</v>
@@ -19063,7 +19063,7 @@
         <v>57</v>
       </c>
       <c r="K310" s="7">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="L310" s="8" t="s">
         <v>47</v>
@@ -19101,7 +19101,7 @@
         <v>46</v>
       </c>
       <c r="K311" s="9">
-        <v>47</v>
+        <v>344</v>
       </c>
       <c r="L311" s="8" t="s">
         <v>47</v>
@@ -19139,7 +19139,7 @@
         <v>52</v>
       </c>
       <c r="K312" s="7">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="L312" s="8" t="s">
         <v>47</v>
@@ -19177,7 +19177,7 @@
         <v>57</v>
       </c>
       <c r="K313" s="9">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="L313" s="8" t="s">
         <v>47</v>
@@ -19215,7 +19215,7 @@
         <v>46</v>
       </c>
       <c r="K314" s="7">
-        <v>114</v>
+        <v>431</v>
       </c>
       <c r="L314" s="8" t="s">
         <v>47</v>
@@ -19253,7 +19253,7 @@
         <v>52</v>
       </c>
       <c r="K315" s="9">
-        <v>270</v>
+        <v>465</v>
       </c>
       <c r="L315" s="8" t="s">
         <v>47</v>
@@ -19291,7 +19291,7 @@
         <v>57</v>
       </c>
       <c r="K316" s="7">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="L316" s="8" t="s">
         <v>47</v>
@@ -19329,7 +19329,7 @@
         <v>46</v>
       </c>
       <c r="K317" s="9">
-        <v>293</v>
+        <v>419</v>
       </c>
       <c r="L317" s="8" t="s">
         <v>47</v>
@@ -19367,7 +19367,7 @@
         <v>52</v>
       </c>
       <c r="K318" s="7">
-        <v>191</v>
+        <v>395</v>
       </c>
       <c r="L318" s="8" t="s">
         <v>47</v>
@@ -19405,7 +19405,7 @@
         <v>57</v>
       </c>
       <c r="K319" s="9">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="L319" s="8" t="s">
         <v>47</v>
@@ -19443,7 +19443,7 @@
         <v>46</v>
       </c>
       <c r="K320" s="7">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="L320" s="8" t="s">
         <v>47</v>
@@ -19481,7 +19481,7 @@
         <v>52</v>
       </c>
       <c r="K321" s="9">
-        <v>326</v>
+        <v>125</v>
       </c>
       <c r="L321" s="8" t="s">
         <v>47</v>
@@ -19519,7 +19519,7 @@
         <v>57</v>
       </c>
       <c r="K322" s="7">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="L322" s="8" t="s">
         <v>47</v>
@@ -19557,7 +19557,7 @@
         <v>46</v>
       </c>
       <c r="K323" s="9">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="L323" s="8" t="s">
         <v>47</v>
@@ -19595,7 +19595,7 @@
         <v>52</v>
       </c>
       <c r="K324" s="7">
-        <v>455</v>
+        <v>307</v>
       </c>
       <c r="L324" s="8" t="s">
         <v>47</v>
@@ -19633,7 +19633,7 @@
         <v>57</v>
       </c>
       <c r="K325" s="9">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="L325" s="8" t="s">
         <v>47</v>
@@ -19671,7 +19671,7 @@
         <v>46</v>
       </c>
       <c r="K326" s="7">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="L326" s="8" t="s">
         <v>47</v>
@@ -19709,7 +19709,7 @@
         <v>52</v>
       </c>
       <c r="K327" s="9">
-        <v>426</v>
+        <v>29</v>
       </c>
       <c r="L327" s="8" t="s">
         <v>47</v>
@@ -19747,7 +19747,7 @@
         <v>57</v>
       </c>
       <c r="K328" s="7">
-        <v>88</v>
+        <v>429</v>
       </c>
       <c r="L328" s="8" t="s">
         <v>47</v>
@@ -19785,7 +19785,7 @@
         <v>46</v>
       </c>
       <c r="K329" s="9">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="L329" s="8" t="s">
         <v>47</v>
@@ -19823,7 +19823,7 @@
         <v>52</v>
       </c>
       <c r="K330" s="7">
-        <v>413</v>
+        <v>143</v>
       </c>
       <c r="L330" s="8" t="s">
         <v>47</v>
@@ -19861,7 +19861,7 @@
         <v>57</v>
       </c>
       <c r="K331" s="9">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="L331" s="8" t="s">
         <v>47</v>
@@ -19899,7 +19899,7 @@
         <v>46</v>
       </c>
       <c r="K332" s="7">
-        <v>233</v>
+        <v>451</v>
       </c>
       <c r="L332" s="8" t="s">
         <v>47</v>
@@ -19937,7 +19937,7 @@
         <v>52</v>
       </c>
       <c r="K333" s="9">
-        <v>399</v>
+        <v>266</v>
       </c>
       <c r="L333" s="8" t="s">
         <v>47</v>
@@ -19975,7 +19975,7 @@
         <v>57</v>
       </c>
       <c r="K334" s="7">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="L334" s="10" t="s">
         <v>162</v>
@@ -20013,7 +20013,7 @@
         <v>46</v>
       </c>
       <c r="K335" s="9">
-        <v>339</v>
+        <v>71</v>
       </c>
       <c r="L335" s="8" t="s">
         <v>47</v>
@@ -20051,7 +20051,7 @@
         <v>52</v>
       </c>
       <c r="K336" s="7">
-        <v>283</v>
+        <v>167</v>
       </c>
       <c r="L336" s="11" t="s">
         <v>253</v>
@@ -20089,7 +20089,7 @@
         <v>57</v>
       </c>
       <c r="K337" s="9">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="L337" s="8" t="s">
         <v>47</v>
@@ -20127,7 +20127,7 @@
         <v>46</v>
       </c>
       <c r="K338" s="7">
-        <v>210</v>
+        <v>421</v>
       </c>
       <c r="L338" s="8" t="s">
         <v>47</v>
@@ -20165,7 +20165,7 @@
         <v>52</v>
       </c>
       <c r="K339" s="9">
-        <v>293</v>
+        <v>453</v>
       </c>
       <c r="L339" s="8" t="s">
         <v>47</v>
@@ -20203,7 +20203,7 @@
         <v>57</v>
       </c>
       <c r="K340" s="7">
-        <v>425</v>
+        <v>95</v>
       </c>
       <c r="L340" s="8" t="s">
         <v>47</v>
@@ -20241,7 +20241,7 @@
         <v>46</v>
       </c>
       <c r="K341" s="9">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="L341" s="8" t="s">
         <v>47</v>
@@ -20279,7 +20279,7 @@
         <v>52</v>
       </c>
       <c r="K342" s="7">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="L342" s="8" t="s">
         <v>47</v>
@@ -20317,7 +20317,7 @@
         <v>57</v>
       </c>
       <c r="K343" s="9">
-        <v>462</v>
+        <v>417</v>
       </c>
       <c r="L343" s="8" t="s">
         <v>47</v>
@@ -20355,7 +20355,7 @@
         <v>46</v>
       </c>
       <c r="K344" s="7">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="L344" s="8" t="s">
         <v>47</v>
@@ -20393,7 +20393,7 @@
         <v>52</v>
       </c>
       <c r="K345" s="9">
-        <v>95</v>
+        <v>414</v>
       </c>
       <c r="L345" s="8" t="s">
         <v>47</v>
@@ -20431,7 +20431,7 @@
         <v>57</v>
       </c>
       <c r="K346" s="7">
-        <v>298</v>
+        <v>85</v>
       </c>
       <c r="L346" s="8" t="s">
         <v>47</v>
@@ -20469,7 +20469,7 @@
         <v>46</v>
       </c>
       <c r="K347" s="9">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L347" s="8" t="s">
         <v>47</v>
@@ -20507,7 +20507,7 @@
         <v>52</v>
       </c>
       <c r="K348" s="7">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="L348" s="8" t="s">
         <v>47</v>
@@ -20545,7 +20545,7 @@
         <v>57</v>
       </c>
       <c r="K349" s="9">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="L349" s="8" t="s">
         <v>47</v>
@@ -20583,7 +20583,7 @@
         <v>46</v>
       </c>
       <c r="K350" s="7">
-        <v>406</v>
+        <v>54</v>
       </c>
       <c r="L350" s="8" t="s">
         <v>47</v>
@@ -20621,7 +20621,7 @@
         <v>52</v>
       </c>
       <c r="K351" s="9">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="L351" s="8" t="s">
         <v>47</v>
@@ -20659,7 +20659,7 @@
         <v>57</v>
       </c>
       <c r="K352" s="7">
-        <v>65</v>
+        <v>268</v>
       </c>
       <c r="L352" s="8" t="s">
         <v>47</v>
@@ -20697,7 +20697,7 @@
         <v>46</v>
       </c>
       <c r="K353" s="9">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="L353" s="8" t="s">
         <v>47</v>
@@ -20735,7 +20735,7 @@
         <v>52</v>
       </c>
       <c r="K354" s="7">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="L354" s="8" t="s">
         <v>47</v>
@@ -20773,7 +20773,7 @@
         <v>57</v>
       </c>
       <c r="K355" s="9">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="L355" s="8" t="s">
         <v>47</v>
@@ -20811,7 +20811,7 @@
         <v>46</v>
       </c>
       <c r="K356" s="7">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="L356" s="8" t="s">
         <v>47</v>
@@ -20849,7 +20849,7 @@
         <v>52</v>
       </c>
       <c r="K357" s="9">
-        <v>429</v>
+        <v>334</v>
       </c>
       <c r="L357" s="8" t="s">
         <v>47</v>
@@ -20887,7 +20887,7 @@
         <v>57</v>
       </c>
       <c r="K358" s="7">
-        <v>182</v>
+        <v>377</v>
       </c>
       <c r="L358" s="8" t="s">
         <v>47</v>
@@ -20925,7 +20925,7 @@
         <v>46</v>
       </c>
       <c r="K359" s="9">
-        <v>253</v>
+        <v>456</v>
       </c>
       <c r="L359" s="8" t="s">
         <v>47</v>
@@ -20963,7 +20963,7 @@
         <v>52</v>
       </c>
       <c r="K360" s="7">
-        <v>205</v>
+        <v>379</v>
       </c>
       <c r="L360" s="8" t="s">
         <v>47</v>
@@ -21001,7 +21001,7 @@
         <v>57</v>
       </c>
       <c r="K361" s="9">
-        <v>133</v>
+        <v>385</v>
       </c>
       <c r="L361" s="8" t="s">
         <v>47</v>
@@ -21039,7 +21039,7 @@
         <v>46</v>
       </c>
       <c r="K362" s="7">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="L362" s="8" t="s">
         <v>47</v>
@@ -21077,7 +21077,7 @@
         <v>52</v>
       </c>
       <c r="K363" s="9">
-        <v>222</v>
+        <v>381</v>
       </c>
       <c r="L363" s="8" t="s">
         <v>47</v>
@@ -21115,7 +21115,7 @@
         <v>57</v>
       </c>
       <c r="K364" s="7">
-        <v>396</v>
+        <v>213</v>
       </c>
       <c r="L364" s="8" t="s">
         <v>47</v>
@@ -21153,7 +21153,7 @@
         <v>46</v>
       </c>
       <c r="K365" s="9">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="L365" s="8" t="s">
         <v>47</v>
@@ -21191,7 +21191,7 @@
         <v>52</v>
       </c>
       <c r="K366" s="7">
-        <v>401</v>
+        <v>184</v>
       </c>
       <c r="L366" s="8" t="s">
         <v>47</v>
@@ -21229,7 +21229,7 @@
         <v>57</v>
       </c>
       <c r="K367" s="9">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="L367" s="8" t="s">
         <v>47</v>
@@ -21267,7 +21267,7 @@
         <v>46</v>
       </c>
       <c r="K368" s="7">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="L368" s="8" t="s">
         <v>47</v>
@@ -21305,7 +21305,7 @@
         <v>52</v>
       </c>
       <c r="K369" s="9">
-        <v>351</v>
+        <v>65</v>
       </c>
       <c r="L369" s="8" t="s">
         <v>47</v>
@@ -21343,7 +21343,7 @@
         <v>57</v>
       </c>
       <c r="K370" s="7">
-        <v>363</v>
+        <v>308</v>
       </c>
       <c r="L370" s="8" t="s">
         <v>47</v>
@@ -21381,7 +21381,7 @@
         <v>46</v>
       </c>
       <c r="K371" s="9">
-        <v>70</v>
+        <v>357</v>
       </c>
       <c r="L371" s="10" t="s">
         <v>162</v>
@@ -21419,7 +21419,7 @@
         <v>52</v>
       </c>
       <c r="K372" s="7">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="L372" s="8" t="s">
         <v>47</v>
@@ -21457,7 +21457,7 @@
         <v>57</v>
       </c>
       <c r="K373" s="9">
-        <v>346</v>
+        <v>20</v>
       </c>
       <c r="L373" s="8" t="s">
         <v>47</v>
@@ -21495,7 +21495,7 @@
         <v>46</v>
       </c>
       <c r="K374" s="7">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="L374" s="8" t="s">
         <v>47</v>
@@ -21533,7 +21533,7 @@
         <v>52</v>
       </c>
       <c r="K375" s="9">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L375" s="8" t="s">
         <v>47</v>
@@ -21571,7 +21571,7 @@
         <v>57</v>
       </c>
       <c r="K376" s="7">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="L376" s="8" t="s">
         <v>47</v>
@@ -21609,7 +21609,7 @@
         <v>46</v>
       </c>
       <c r="K377" s="9">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="L377" s="8" t="s">
         <v>47</v>
@@ -21647,7 +21647,7 @@
         <v>52</v>
       </c>
       <c r="K378" s="7">
-        <v>117</v>
+        <v>323</v>
       </c>
       <c r="L378" s="8" t="s">
         <v>47</v>
@@ -21685,7 +21685,7 @@
         <v>57</v>
       </c>
       <c r="K379" s="9">
-        <v>39</v>
+        <v>343</v>
       </c>
       <c r="L379" s="8" t="s">
         <v>47</v>
@@ -21723,7 +21723,7 @@
         <v>46</v>
       </c>
       <c r="K380" s="7">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="L380" s="8" t="s">
         <v>47</v>
@@ -21761,7 +21761,7 @@
         <v>52</v>
       </c>
       <c r="K381" s="9">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="L381" s="8" t="s">
         <v>47</v>
@@ -21799,7 +21799,7 @@
         <v>57</v>
       </c>
       <c r="K382" s="7">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="L382" s="8" t="s">
         <v>47</v>
@@ -21837,7 +21837,7 @@
         <v>46</v>
       </c>
       <c r="K383" s="9">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="L383" s="8" t="s">
         <v>47</v>
@@ -21875,7 +21875,7 @@
         <v>52</v>
       </c>
       <c r="K384" s="7">
-        <v>132</v>
+        <v>442</v>
       </c>
       <c r="L384" s="8" t="s">
         <v>47</v>
@@ -21913,7 +21913,7 @@
         <v>57</v>
       </c>
       <c r="K385" s="9">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="L385" s="8" t="s">
         <v>47</v>
@@ -21951,7 +21951,7 @@
         <v>46</v>
       </c>
       <c r="K386" s="7">
-        <v>416</v>
+        <v>66</v>
       </c>
       <c r="L386" s="8" t="s">
         <v>47</v>
@@ -21989,7 +21989,7 @@
         <v>52</v>
       </c>
       <c r="K387" s="9">
-        <v>104</v>
+        <v>433</v>
       </c>
       <c r="L387" s="8" t="s">
         <v>47</v>
@@ -22027,7 +22027,7 @@
         <v>57</v>
       </c>
       <c r="K388" s="7">
-        <v>320</v>
+        <v>402</v>
       </c>
       <c r="L388" s="8" t="s">
         <v>47</v>
@@ -22065,7 +22065,7 @@
         <v>46</v>
       </c>
       <c r="K389" s="9">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="L389" s="8" t="s">
         <v>47</v>
@@ -22103,7 +22103,7 @@
         <v>52</v>
       </c>
       <c r="K390" s="7">
-        <v>240</v>
+        <v>344</v>
       </c>
       <c r="L390" s="8" t="s">
         <v>47</v>
@@ -22141,7 +22141,7 @@
         <v>57</v>
       </c>
       <c r="K391" s="9">
-        <v>47</v>
+        <v>400</v>
       </c>
       <c r="L391" s="8" t="s">
         <v>47</v>
@@ -22179,7 +22179,7 @@
         <v>46</v>
       </c>
       <c r="K392" s="7">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="L392" s="8" t="s">
         <v>47</v>
@@ -22217,7 +22217,7 @@
         <v>52</v>
       </c>
       <c r="K393" s="9">
-        <v>131</v>
+        <v>376</v>
       </c>
       <c r="L393" s="8" t="s">
         <v>47</v>
@@ -22255,7 +22255,7 @@
         <v>57</v>
       </c>
       <c r="K394" s="7">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="L394" s="8" t="s">
         <v>47</v>
@@ -22293,7 +22293,7 @@
         <v>46</v>
       </c>
       <c r="K395" s="9">
-        <v>159</v>
+        <v>419</v>
       </c>
       <c r="L395" s="8" t="s">
         <v>47</v>
@@ -22331,7 +22331,7 @@
         <v>52</v>
       </c>
       <c r="K396" s="7">
-        <v>121</v>
+        <v>381</v>
       </c>
       <c r="L396" s="8" t="s">
         <v>47</v>
@@ -22369,7 +22369,7 @@
         <v>57</v>
       </c>
       <c r="K397" s="9">
-        <v>62</v>
+        <v>380</v>
       </c>
       <c r="L397" s="8" t="s">
         <v>47</v>
@@ -22445,7 +22445,7 @@
         <v>52</v>
       </c>
       <c r="K399" s="9">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="L399" s="8" t="s">
         <v>47</v>
@@ -22483,7 +22483,7 @@
         <v>57</v>
       </c>
       <c r="K400" s="7">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="L400" s="8" t="s">
         <v>47</v>
@@ -22521,7 +22521,7 @@
         <v>46</v>
       </c>
       <c r="K401" s="9">
-        <v>448</v>
+        <v>173</v>
       </c>
       <c r="L401" s="8" t="s">
         <v>47</v>
@@ -22559,7 +22559,7 @@
         <v>52</v>
       </c>
       <c r="K402" s="7">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="L402" s="8" t="s">
         <v>47</v>
@@ -22597,7 +22597,7 @@
         <v>57</v>
       </c>
       <c r="K403" s="9">
-        <v>208</v>
+        <v>147</v>
       </c>
       <c r="L403" s="11" t="s">
         <v>253</v>
@@ -22635,7 +22635,7 @@
         <v>46</v>
       </c>
       <c r="K404" s="7">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="L404" s="8" t="s">
         <v>47</v>
@@ -22673,7 +22673,7 @@
         <v>52</v>
       </c>
       <c r="K405" s="9">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="L405" s="8" t="s">
         <v>47</v>
@@ -22711,7 +22711,7 @@
         <v>57</v>
       </c>
       <c r="K406" s="7">
-        <v>453</v>
+        <v>48</v>
       </c>
       <c r="L406" s="8" t="s">
         <v>47</v>
@@ -22749,7 +22749,7 @@
         <v>46</v>
       </c>
       <c r="K407" s="9">
-        <v>51</v>
+        <v>340</v>
       </c>
       <c r="L407" s="8" t="s">
         <v>47</v>
@@ -22787,7 +22787,7 @@
         <v>52</v>
       </c>
       <c r="K408" s="7">
-        <v>210</v>
+        <v>263</v>
       </c>
       <c r="L408" s="10" t="s">
         <v>162</v>
@@ -22825,7 +22825,7 @@
         <v>57</v>
       </c>
       <c r="K409" s="9">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="L409" s="8" t="s">
         <v>47</v>
@@ -22863,7 +22863,7 @@
         <v>46</v>
       </c>
       <c r="K410" s="7">
-        <v>207</v>
+        <v>469</v>
       </c>
       <c r="L410" s="8" t="s">
         <v>47</v>
@@ -22901,7 +22901,7 @@
         <v>52</v>
       </c>
       <c r="K411" s="9">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="L411" s="8" t="s">
         <v>47</v>
@@ -22939,7 +22939,7 @@
         <v>57</v>
       </c>
       <c r="K412" s="7">
-        <v>347</v>
+        <v>172</v>
       </c>
       <c r="L412" s="8" t="s">
         <v>47</v>
@@ -22977,7 +22977,7 @@
         <v>46</v>
       </c>
       <c r="K413" s="9">
-        <v>331</v>
+        <v>251</v>
       </c>
       <c r="L413" s="8" t="s">
         <v>47</v>
@@ -23015,7 +23015,7 @@
         <v>52</v>
       </c>
       <c r="K414" s="7">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="L414" s="8" t="s">
         <v>47</v>
@@ -23053,7 +23053,7 @@
         <v>57</v>
       </c>
       <c r="K415" s="9">
-        <v>367</v>
+        <v>441</v>
       </c>
       <c r="L415" s="8" t="s">
         <v>47</v>
@@ -23091,7 +23091,7 @@
         <v>46</v>
       </c>
       <c r="K416" s="7">
-        <v>362</v>
+        <v>186</v>
       </c>
       <c r="L416" s="8" t="s">
         <v>47</v>
@@ -23129,7 +23129,7 @@
         <v>52</v>
       </c>
       <c r="K417" s="9">
-        <v>314</v>
+        <v>38</v>
       </c>
       <c r="L417" s="8" t="s">
         <v>47</v>
@@ -23167,7 +23167,7 @@
         <v>57</v>
       </c>
       <c r="K418" s="7">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="L418" s="8" t="s">
         <v>47</v>
@@ -23205,7 +23205,7 @@
         <v>46</v>
       </c>
       <c r="K419" s="9">
-        <v>254</v>
+        <v>397</v>
       </c>
       <c r="L419" s="8" t="s">
         <v>47</v>
@@ -23243,7 +23243,7 @@
         <v>52</v>
       </c>
       <c r="K420" s="7">
-        <v>399</v>
+        <v>341</v>
       </c>
       <c r="L420" s="8" t="s">
         <v>47</v>
@@ -23281,7 +23281,7 @@
         <v>57</v>
       </c>
       <c r="K421" s="9">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="L421" s="8" t="s">
         <v>47</v>
@@ -23319,7 +23319,7 @@
         <v>46</v>
       </c>
       <c r="K422" s="7">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="L422" s="8" t="s">
         <v>47</v>
@@ -23357,7 +23357,7 @@
         <v>52</v>
       </c>
       <c r="K423" s="9">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="L423" s="8" t="s">
         <v>47</v>
@@ -23395,7 +23395,7 @@
         <v>57</v>
       </c>
       <c r="K424" s="7">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="L424" s="8" t="s">
         <v>47</v>
@@ -23433,7 +23433,7 @@
         <v>46</v>
       </c>
       <c r="K425" s="9">
-        <v>67</v>
+        <v>327</v>
       </c>
       <c r="L425" s="8" t="s">
         <v>47</v>
@@ -23471,7 +23471,7 @@
         <v>52</v>
       </c>
       <c r="K426" s="7">
-        <v>230</v>
+        <v>101</v>
       </c>
       <c r="L426" s="8" t="s">
         <v>47</v>
@@ -23509,7 +23509,7 @@
         <v>57</v>
       </c>
       <c r="K427" s="9">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="L427" s="8" t="s">
         <v>47</v>
@@ -23547,7 +23547,7 @@
         <v>46</v>
       </c>
       <c r="K428" s="7">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="L428" s="8" t="s">
         <v>47</v>
@@ -23585,7 +23585,7 @@
         <v>52</v>
       </c>
       <c r="K429" s="9">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="L429" s="8" t="s">
         <v>47</v>
@@ -23623,7 +23623,7 @@
         <v>57</v>
       </c>
       <c r="K430" s="7">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="L430" s="8" t="s">
         <v>47</v>
@@ -23661,7 +23661,7 @@
         <v>46</v>
       </c>
       <c r="K431" s="9">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="L431" s="8" t="s">
         <v>47</v>
@@ -23699,7 +23699,7 @@
         <v>52</v>
       </c>
       <c r="K432" s="7">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="L432" s="8" t="s">
         <v>47</v>
@@ -23737,7 +23737,7 @@
         <v>57</v>
       </c>
       <c r="K433" s="9">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="L433" s="8" t="s">
         <v>47</v>
@@ -23775,7 +23775,7 @@
         <v>46</v>
       </c>
       <c r="K434" s="7">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="L434" s="8" t="s">
         <v>47</v>
@@ -23813,7 +23813,7 @@
         <v>52</v>
       </c>
       <c r="K435" s="9">
-        <v>39</v>
+        <v>466</v>
       </c>
       <c r="L435" s="8" t="s">
         <v>47</v>
@@ -23851,7 +23851,7 @@
         <v>57</v>
       </c>
       <c r="K436" s="7">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="L436" s="8" t="s">
         <v>47</v>
@@ -23889,7 +23889,7 @@
         <v>46</v>
       </c>
       <c r="K437" s="9">
-        <v>58</v>
+        <v>404</v>
       </c>
       <c r="L437" s="8" t="s">
         <v>47</v>
@@ -23927,7 +23927,7 @@
         <v>52</v>
       </c>
       <c r="K438" s="7">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="L438" s="8" t="s">
         <v>47</v>
@@ -23965,7 +23965,7 @@
         <v>57</v>
       </c>
       <c r="K439" s="9">
-        <v>158</v>
+        <v>376</v>
       </c>
       <c r="L439" s="8" t="s">
         <v>47</v>
@@ -24003,7 +24003,7 @@
         <v>46</v>
       </c>
       <c r="K440" s="7">
-        <v>392</v>
+        <v>163</v>
       </c>
       <c r="L440" s="8" t="s">
         <v>47</v>
@@ -24041,7 +24041,7 @@
         <v>52</v>
       </c>
       <c r="K441" s="9">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="L441" s="8" t="s">
         <v>47</v>
@@ -24079,7 +24079,7 @@
         <v>57</v>
       </c>
       <c r="K442" s="7">
-        <v>257</v>
+        <v>27</v>
       </c>
       <c r="L442" s="8" t="s">
         <v>47</v>
@@ -24117,7 +24117,7 @@
         <v>46</v>
       </c>
       <c r="K443" s="9">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="L443" s="8" t="s">
         <v>47</v>
@@ -24155,7 +24155,7 @@
         <v>52</v>
       </c>
       <c r="K444" s="7">
-        <v>389</v>
+        <v>105</v>
       </c>
       <c r="L444" s="8" t="s">
         <v>47</v>
@@ -24193,7 +24193,7 @@
         <v>57</v>
       </c>
       <c r="K445" s="9">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L445" s="10" t="s">
         <v>162</v>
@@ -24231,7 +24231,7 @@
         <v>46</v>
       </c>
       <c r="K446" s="7">
-        <v>127</v>
+        <v>344</v>
       </c>
       <c r="L446" s="8" t="s">
         <v>47</v>
@@ -24269,7 +24269,7 @@
         <v>52</v>
       </c>
       <c r="K447" s="9">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="L447" s="8" t="s">
         <v>47</v>
@@ -24307,7 +24307,7 @@
         <v>57</v>
       </c>
       <c r="K448" s="7">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="L448" s="8" t="s">
         <v>47</v>
@@ -24345,7 +24345,7 @@
         <v>46</v>
       </c>
       <c r="K449" s="9">
-        <v>72</v>
+        <v>159</v>
       </c>
       <c r="L449" s="8" t="s">
         <v>47</v>
@@ -24383,7 +24383,7 @@
         <v>52</v>
       </c>
       <c r="K450" s="7">
-        <v>427</v>
+        <v>74</v>
       </c>
       <c r="L450" s="8" t="s">
         <v>47</v>
@@ -24421,7 +24421,7 @@
         <v>57</v>
       </c>
       <c r="K451" s="9">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="L451" s="8" t="s">
         <v>47</v>
@@ -24459,7 +24459,7 @@
         <v>46</v>
       </c>
       <c r="K452" s="7">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="L452" s="8" t="s">
         <v>47</v>
@@ -24497,7 +24497,7 @@
         <v>52</v>
       </c>
       <c r="K453" s="9">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="L453" s="8" t="s">
         <v>47</v>
@@ -24535,7 +24535,7 @@
         <v>57</v>
       </c>
       <c r="K454" s="7">
-        <v>180</v>
+        <v>467</v>
       </c>
       <c r="L454" s="8" t="s">
         <v>47</v>
@@ -24573,7 +24573,7 @@
         <v>46</v>
       </c>
       <c r="K455" s="9">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="L455" s="8" t="s">
         <v>47</v>
@@ -24611,7 +24611,7 @@
         <v>52</v>
       </c>
       <c r="K456" s="7">
-        <v>97</v>
+        <v>426</v>
       </c>
       <c r="L456" s="8" t="s">
         <v>47</v>
@@ -24649,7 +24649,7 @@
         <v>57</v>
       </c>
       <c r="K457" s="9">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="L457" s="8" t="s">
         <v>47</v>
@@ -24687,7 +24687,7 @@
         <v>46</v>
       </c>
       <c r="K458" s="7">
-        <v>406</v>
+        <v>270</v>
       </c>
       <c r="L458" s="8" t="s">
         <v>47</v>
@@ -24725,7 +24725,7 @@
         <v>52</v>
       </c>
       <c r="K459" s="9">
-        <v>459</v>
+        <v>194</v>
       </c>
       <c r="L459" s="8" t="s">
         <v>47</v>
@@ -24763,7 +24763,7 @@
         <v>57</v>
       </c>
       <c r="K460" s="7">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="L460" s="8" t="s">
         <v>47</v>
@@ -24801,7 +24801,7 @@
         <v>46</v>
       </c>
       <c r="K461" s="9">
-        <v>134</v>
+        <v>462</v>
       </c>
       <c r="L461" s="8" t="s">
         <v>47</v>
@@ -24839,7 +24839,7 @@
         <v>52</v>
       </c>
       <c r="K462" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L462" s="8" t="s">
         <v>47</v>
@@ -24877,7 +24877,7 @@
         <v>57</v>
       </c>
       <c r="K463" s="9">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="L463" s="8" t="s">
         <v>47</v>
@@ -24915,7 +24915,7 @@
         <v>46</v>
       </c>
       <c r="K464" s="7">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="L464" s="8" t="s">
         <v>47</v>
@@ -24953,7 +24953,7 @@
         <v>52</v>
       </c>
       <c r="K465" s="9">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="L465" s="8" t="s">
         <v>47</v>
@@ -24991,7 +24991,7 @@
         <v>57</v>
       </c>
       <c r="K466" s="7">
-        <v>81</v>
+        <v>439</v>
       </c>
       <c r="L466" s="8" t="s">
         <v>47</v>
@@ -25029,7 +25029,7 @@
         <v>46</v>
       </c>
       <c r="K467" s="9">
-        <v>207</v>
+        <v>60</v>
       </c>
       <c r="L467" s="8" t="s">
         <v>47</v>
@@ -25067,7 +25067,7 @@
         <v>52</v>
       </c>
       <c r="K468" s="7">
-        <v>399</v>
+        <v>163</v>
       </c>
       <c r="L468" s="8" t="s">
         <v>47</v>
@@ -25105,7 +25105,7 @@
         <v>57</v>
       </c>
       <c r="K469" s="9">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="L469" s="8" t="s">
         <v>47</v>
@@ -25143,7 +25143,7 @@
         <v>46</v>
       </c>
       <c r="K470" s="7">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="L470" s="11" t="s">
         <v>253</v>
@@ -25181,7 +25181,7 @@
         <v>52</v>
       </c>
       <c r="K471" s="9">
-        <v>453</v>
+        <v>216</v>
       </c>
       <c r="L471" s="8" t="s">
         <v>47</v>
@@ -25219,7 +25219,7 @@
         <v>57</v>
       </c>
       <c r="K472" s="7">
-        <v>56</v>
+        <v>394</v>
       </c>
       <c r="L472" s="8" t="s">
         <v>47</v>
@@ -25257,7 +25257,7 @@
         <v>46</v>
       </c>
       <c r="K473" s="9">
-        <v>144</v>
+        <v>291</v>
       </c>
       <c r="L473" s="8" t="s">
         <v>47</v>
@@ -25295,7 +25295,7 @@
         <v>52</v>
       </c>
       <c r="K474" s="7">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="L474" s="8" t="s">
         <v>47</v>
@@ -25333,7 +25333,7 @@
         <v>57</v>
       </c>
       <c r="K475" s="9">
-        <v>201</v>
+        <v>332</v>
       </c>
       <c r="L475" s="8" t="s">
         <v>47</v>
@@ -25371,7 +25371,7 @@
         <v>46</v>
       </c>
       <c r="K476" s="7">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L476" s="8" t="s">
         <v>47</v>
@@ -25409,7 +25409,7 @@
         <v>52</v>
       </c>
       <c r="K477" s="9">
-        <v>85</v>
+        <v>403</v>
       </c>
       <c r="L477" s="8" t="s">
         <v>47</v>
@@ -25447,7 +25447,7 @@
         <v>57</v>
       </c>
       <c r="K478" s="7">
-        <v>396</v>
+        <v>68</v>
       </c>
       <c r="L478" s="8" t="s">
         <v>47</v>
@@ -25485,7 +25485,7 @@
         <v>46</v>
       </c>
       <c r="K479" s="9">
-        <v>281</v>
+        <v>197</v>
       </c>
       <c r="L479" s="8" t="s">
         <v>47</v>
@@ -25523,7 +25523,7 @@
         <v>52</v>
       </c>
       <c r="K480" s="7">
-        <v>390</v>
+        <v>159</v>
       </c>
       <c r="L480" s="8" t="s">
         <v>47</v>
@@ -25561,7 +25561,7 @@
         <v>57</v>
       </c>
       <c r="K481" s="9">
-        <v>124</v>
+        <v>388</v>
       </c>
       <c r="L481" s="8" t="s">
         <v>47</v>
@@ -25599,7 +25599,7 @@
         <v>46</v>
       </c>
       <c r="K482" s="7">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="L482" s="10" t="s">
         <v>162</v>
@@ -25637,7 +25637,7 @@
         <v>52</v>
       </c>
       <c r="K483" s="9">
-        <v>150</v>
+        <v>376</v>
       </c>
       <c r="L483" s="8" t="s">
         <v>47</v>
@@ -25675,7 +25675,7 @@
         <v>57</v>
       </c>
       <c r="K484" s="7">
-        <v>445</v>
+        <v>240</v>
       </c>
       <c r="L484" s="8" t="s">
         <v>47</v>
@@ -25713,7 +25713,7 @@
         <v>46</v>
       </c>
       <c r="K485" s="9">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="L485" s="8" t="s">
         <v>47</v>
@@ -25751,7 +25751,7 @@
         <v>52</v>
       </c>
       <c r="K486" s="7">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="L486" s="8" t="s">
         <v>47</v>
@@ -25789,7 +25789,7 @@
         <v>57</v>
       </c>
       <c r="K487" s="9">
-        <v>454</v>
+        <v>67</v>
       </c>
       <c r="L487" s="8" t="s">
         <v>47</v>
@@ -25827,7 +25827,7 @@
         <v>46</v>
       </c>
       <c r="K488" s="7">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L488" s="8" t="s">
         <v>47</v>
@@ -25865,7 +25865,7 @@
         <v>52</v>
       </c>
       <c r="K489" s="9">
-        <v>36</v>
+        <v>428</v>
       </c>
       <c r="L489" s="8" t="s">
         <v>47</v>
@@ -25903,7 +25903,7 @@
         <v>57</v>
       </c>
       <c r="K490" s="7">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="L490" s="8" t="s">
         <v>47</v>
@@ -25941,7 +25941,7 @@
         <v>46</v>
       </c>
       <c r="K491" s="9">
-        <v>271</v>
+        <v>68</v>
       </c>
       <c r="L491" s="8" t="s">
         <v>47</v>
@@ -25979,7 +25979,7 @@
         <v>52</v>
       </c>
       <c r="K492" s="7">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L492" s="8" t="s">
         <v>47</v>
@@ -26017,7 +26017,7 @@
         <v>57</v>
       </c>
       <c r="K493" s="9">
-        <v>253</v>
+        <v>33</v>
       </c>
       <c r="L493" s="8" t="s">
         <v>47</v>
@@ -26055,7 +26055,7 @@
         <v>46</v>
       </c>
       <c r="K494" s="7">
-        <v>66</v>
+        <v>438</v>
       </c>
       <c r="L494" s="8" t="s">
         <v>47</v>
@@ -26093,7 +26093,7 @@
         <v>52</v>
       </c>
       <c r="K495" s="9">
-        <v>35</v>
+        <v>212</v>
       </c>
       <c r="L495" s="8" t="s">
         <v>47</v>
@@ -26131,7 +26131,7 @@
         <v>57</v>
       </c>
       <c r="K496" s="7">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="L496" s="8" t="s">
         <v>47</v>
@@ -26169,7 +26169,7 @@
         <v>46</v>
       </c>
       <c r="K497" s="9">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="L497" s="8" t="s">
         <v>47</v>
@@ -26207,7 +26207,7 @@
         <v>52</v>
       </c>
       <c r="K498" s="7">
-        <v>362</v>
+        <v>110</v>
       </c>
       <c r="L498" s="8" t="s">
         <v>47</v>
@@ -26245,7 +26245,7 @@
         <v>57</v>
       </c>
       <c r="K499" s="9">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L499" s="8" t="s">
         <v>47</v>
@@ -26283,7 +26283,7 @@
         <v>46</v>
       </c>
       <c r="K500" s="7">
-        <v>235</v>
+        <v>342</v>
       </c>
       <c r="L500" s="8" t="s">
         <v>47</v>
@@ -26321,7 +26321,7 @@
         <v>52</v>
       </c>
       <c r="K501" s="9">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="L501" s="8" t="s">
         <v>47</v>
@@ -26359,7 +26359,7 @@
         <v>57</v>
       </c>
       <c r="K502" s="7">
-        <v>269</v>
+        <v>448</v>
       </c>
       <c r="L502" s="8" t="s">
         <v>47</v>
@@ -26397,7 +26397,7 @@
         <v>46</v>
       </c>
       <c r="K503" s="9">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="L503" s="8" t="s">
         <v>47</v>
@@ -26435,7 +26435,7 @@
         <v>52</v>
       </c>
       <c r="K504" s="7">
-        <v>64</v>
+        <v>310</v>
       </c>
       <c r="L504" s="8" t="s">
         <v>47</v>
@@ -26473,7 +26473,7 @@
         <v>57</v>
       </c>
       <c r="K505" s="9">
-        <v>32</v>
+        <v>436</v>
       </c>
       <c r="L505" s="8" t="s">
         <v>47</v>
@@ -26511,7 +26511,7 @@
         <v>46</v>
       </c>
       <c r="K506" s="7">
-        <v>307</v>
+        <v>240</v>
       </c>
       <c r="L506" s="8" t="s">
         <v>47</v>
@@ -26549,7 +26549,7 @@
         <v>52</v>
       </c>
       <c r="K507" s="9">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="L507" s="8" t="s">
         <v>47</v>
@@ -26587,7 +26587,7 @@
         <v>57</v>
       </c>
       <c r="K508" s="7">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="L508" s="8" t="s">
         <v>47</v>
@@ -26625,7 +26625,7 @@
         <v>46</v>
       </c>
       <c r="K509" s="9">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="L509" s="8" t="s">
         <v>47</v>
@@ -26663,7 +26663,7 @@
         <v>52</v>
       </c>
       <c r="K510" s="7">
-        <v>313</v>
+        <v>439</v>
       </c>
       <c r="L510" s="8" t="s">
         <v>47</v>
@@ -26701,7 +26701,7 @@
         <v>57</v>
       </c>
       <c r="K511" s="9">
-        <v>304</v>
+        <v>179</v>
       </c>
       <c r="L511" s="8" t="s">
         <v>47</v>
@@ -26739,7 +26739,7 @@
         <v>46</v>
       </c>
       <c r="K512" s="7">
-        <v>464</v>
+        <v>68</v>
       </c>
       <c r="L512" s="8" t="s">
         <v>47</v>
@@ -26777,7 +26777,7 @@
         <v>52</v>
       </c>
       <c r="K513" s="9">
-        <v>406</v>
+        <v>197</v>
       </c>
       <c r="L513" s="8" t="s">
         <v>47</v>
@@ -26815,7 +26815,7 @@
         <v>57</v>
       </c>
       <c r="K514" s="7">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="L514" s="8" t="s">
         <v>47</v>
@@ -26853,7 +26853,7 @@
         <v>46</v>
       </c>
       <c r="K515" s="9">
-        <v>151</v>
+        <v>441</v>
       </c>
       <c r="L515" s="8" t="s">
         <v>47</v>
@@ -26891,7 +26891,7 @@
         <v>52</v>
       </c>
       <c r="K516" s="7">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="L516" s="8" t="s">
         <v>47</v>
@@ -26929,7 +26929,7 @@
         <v>57</v>
       </c>
       <c r="K517" s="9">
-        <v>140</v>
+        <v>375</v>
       </c>
       <c r="L517" s="8" t="s">
         <v>47</v>
@@ -26967,7 +26967,7 @@
         <v>46</v>
       </c>
       <c r="K518" s="7">
-        <v>275</v>
+        <v>333</v>
       </c>
       <c r="L518" s="8" t="s">
         <v>47</v>
@@ -27005,7 +27005,7 @@
         <v>52</v>
       </c>
       <c r="K519" s="9">
-        <v>226</v>
+        <v>355</v>
       </c>
       <c r="L519" s="10" t="s">
         <v>162</v>
@@ -27043,7 +27043,7 @@
         <v>57</v>
       </c>
       <c r="K520" s="7">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="L520" s="8" t="s">
         <v>47</v>
@@ -27081,7 +27081,7 @@
         <v>46</v>
       </c>
       <c r="K521" s="9">
-        <v>458</v>
+        <v>66</v>
       </c>
       <c r="L521" s="8" t="s">
         <v>47</v>
@@ -27119,7 +27119,7 @@
         <v>52</v>
       </c>
       <c r="K522" s="7">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="L522" s="8" t="s">
         <v>47</v>
@@ -27157,7 +27157,7 @@
         <v>57</v>
       </c>
       <c r="K523" s="9">
-        <v>337</v>
+        <v>168</v>
       </c>
       <c r="L523" s="8" t="s">
         <v>47</v>
@@ -27195,7 +27195,7 @@
         <v>46</v>
       </c>
       <c r="K524" s="7">
-        <v>394</v>
+        <v>165</v>
       </c>
       <c r="L524" s="8" t="s">
         <v>47</v>
@@ -27233,7 +27233,7 @@
         <v>52</v>
       </c>
       <c r="K525" s="9">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="L525" s="8" t="s">
         <v>47</v>
@@ -27271,7 +27271,7 @@
         <v>57</v>
       </c>
       <c r="K526" s="7">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="L526" s="8" t="s">
         <v>47</v>
@@ -27309,7 +27309,7 @@
         <v>46</v>
       </c>
       <c r="K527" s="9">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="L527" s="8" t="s">
         <v>47</v>
@@ -27347,7 +27347,7 @@
         <v>52</v>
       </c>
       <c r="K528" s="7">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="L528" s="8" t="s">
         <v>47</v>
@@ -27385,7 +27385,7 @@
         <v>57</v>
       </c>
       <c r="K529" s="9">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="L529" s="8" t="s">
         <v>47</v>
@@ -27423,7 +27423,7 @@
         <v>46</v>
       </c>
       <c r="K530" s="7">
-        <v>36</v>
+        <v>392</v>
       </c>
       <c r="L530" s="8" t="s">
         <v>47</v>
@@ -27461,7 +27461,7 @@
         <v>52</v>
       </c>
       <c r="K531" s="9">
-        <v>441</v>
+        <v>259</v>
       </c>
       <c r="L531" s="8" t="s">
         <v>47</v>
@@ -27499,7 +27499,7 @@
         <v>57</v>
       </c>
       <c r="K532" s="7">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="L532" s="8" t="s">
         <v>47</v>
@@ -27537,7 +27537,7 @@
         <v>46</v>
       </c>
       <c r="K533" s="9">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="L533" s="8" t="s">
         <v>47</v>
@@ -27575,7 +27575,7 @@
         <v>52</v>
       </c>
       <c r="K534" s="7">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="L534" s="8" t="s">
         <v>47</v>
@@ -27613,7 +27613,7 @@
         <v>57</v>
       </c>
       <c r="K535" s="9">
-        <v>367</v>
+        <v>280</v>
       </c>
       <c r="L535" s="8" t="s">
         <v>47</v>
@@ -27651,7 +27651,7 @@
         <v>46</v>
       </c>
       <c r="K536" s="7">
-        <v>446</v>
+        <v>359</v>
       </c>
       <c r="L536" s="8" t="s">
         <v>47</v>
@@ -27689,7 +27689,7 @@
         <v>52</v>
       </c>
       <c r="K537" s="9">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="L537" s="11" t="s">
         <v>253</v>
@@ -27727,7 +27727,7 @@
         <v>57</v>
       </c>
       <c r="K538" s="7">
-        <v>436</v>
+        <v>205</v>
       </c>
       <c r="L538" s="8" t="s">
         <v>47</v>
@@ -27765,7 +27765,7 @@
         <v>46</v>
       </c>
       <c r="K539" s="9">
-        <v>228</v>
+        <v>394</v>
       </c>
       <c r="L539" s="8" t="s">
         <v>47</v>
@@ -27803,7 +27803,7 @@
         <v>52</v>
       </c>
       <c r="K540" s="7">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="L540" s="8" t="s">
         <v>47</v>
@@ -27841,7 +27841,7 @@
         <v>57</v>
       </c>
       <c r="K541" s="9">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="L541" s="8" t="s">
         <v>47</v>
@@ -27879,7 +27879,7 @@
         <v>46</v>
       </c>
       <c r="K542" s="7">
-        <v>215</v>
+        <v>334</v>
       </c>
       <c r="L542" s="8" t="s">
         <v>47</v>
@@ -27917,7 +27917,7 @@
         <v>52</v>
       </c>
       <c r="K543" s="9">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="L543" s="8" t="s">
         <v>47</v>
@@ -27955,7 +27955,7 @@
         <v>57</v>
       </c>
       <c r="K544" s="7">
-        <v>176</v>
+        <v>413</v>
       </c>
       <c r="L544" s="8" t="s">
         <v>47</v>
@@ -27993,7 +27993,7 @@
         <v>46</v>
       </c>
       <c r="K545" s="9">
-        <v>356</v>
+        <v>417</v>
       </c>
       <c r="L545" s="8" t="s">
         <v>47</v>
@@ -28031,7 +28031,7 @@
         <v>52</v>
       </c>
       <c r="K546" s="7">
-        <v>300</v>
+        <v>113</v>
       </c>
       <c r="L546" s="8" t="s">
         <v>47</v>
@@ -28069,7 +28069,7 @@
         <v>57</v>
       </c>
       <c r="K547" s="9">
-        <v>321</v>
+        <v>228</v>
       </c>
       <c r="L547" s="8" t="s">
         <v>47</v>
@@ -28107,7 +28107,7 @@
         <v>46</v>
       </c>
       <c r="K548" s="7">
-        <v>357</v>
+        <v>390</v>
       </c>
       <c r="L548" s="8" t="s">
         <v>47</v>
@@ -28145,7 +28145,7 @@
         <v>52</v>
       </c>
       <c r="K549" s="9">
-        <v>349</v>
+        <v>458</v>
       </c>
       <c r="L549" s="8" t="s">
         <v>47</v>
@@ -28183,7 +28183,7 @@
         <v>57</v>
       </c>
       <c r="K550" s="7">
-        <v>183</v>
+        <v>449</v>
       </c>
       <c r="L550" s="8" t="s">
         <v>47</v>
@@ -28221,7 +28221,7 @@
         <v>46</v>
       </c>
       <c r="K551" s="9">
-        <v>258</v>
+        <v>422</v>
       </c>
       <c r="L551" s="8" t="s">
         <v>47</v>
@@ -28259,7 +28259,7 @@
         <v>52</v>
       </c>
       <c r="K552" s="7">
-        <v>263</v>
+        <v>357</v>
       </c>
       <c r="L552" s="8" t="s">
         <v>47</v>
@@ -28297,7 +28297,7 @@
         <v>57</v>
       </c>
       <c r="K553" s="9">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="L553" s="8" t="s">
         <v>47</v>
@@ -28335,7 +28335,7 @@
         <v>46</v>
       </c>
       <c r="K554" s="7">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="L554" s="8" t="s">
         <v>47</v>
@@ -28373,7 +28373,7 @@
         <v>52</v>
       </c>
       <c r="K555" s="9">
-        <v>43</v>
+        <v>428</v>
       </c>
       <c r="L555" s="8" t="s">
         <v>47</v>
@@ -28411,7 +28411,7 @@
         <v>57</v>
       </c>
       <c r="K556" s="7">
-        <v>376</v>
+        <v>425</v>
       </c>
       <c r="L556" s="10" t="s">
         <v>162</v>
@@ -28449,7 +28449,7 @@
         <v>46</v>
       </c>
       <c r="K557" s="9">
-        <v>335</v>
+        <v>138</v>
       </c>
       <c r="L557" s="8" t="s">
         <v>47</v>
@@ -28487,7 +28487,7 @@
         <v>52</v>
       </c>
       <c r="K558" s="7">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="L558" s="8" t="s">
         <v>47</v>
@@ -28525,7 +28525,7 @@
         <v>57</v>
       </c>
       <c r="K559" s="9">
-        <v>438</v>
+        <v>169</v>
       </c>
       <c r="L559" s="8" t="s">
         <v>47</v>
@@ -28563,7 +28563,7 @@
         <v>46</v>
       </c>
       <c r="K560" s="7">
-        <v>397</v>
+        <v>89</v>
       </c>
       <c r="L560" s="8" t="s">
         <v>47</v>
@@ -28601,7 +28601,7 @@
         <v>52</v>
       </c>
       <c r="K561" s="9">
-        <v>377</v>
+        <v>146</v>
       </c>
       <c r="L561" s="8" t="s">
         <v>47</v>
@@ -28639,7 +28639,7 @@
         <v>57</v>
       </c>
       <c r="K562" s="7">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="L562" s="8" t="s">
         <v>47</v>
@@ -28677,7 +28677,7 @@
         <v>46</v>
       </c>
       <c r="K563" s="9">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="L563" s="8" t="s">
         <v>47</v>
@@ -28715,7 +28715,7 @@
         <v>52</v>
       </c>
       <c r="K564" s="7">
-        <v>248</v>
+        <v>133</v>
       </c>
       <c r="L564" s="8" t="s">
         <v>47</v>
@@ -28753,7 +28753,7 @@
         <v>57</v>
       </c>
       <c r="K565" s="9">
-        <v>148</v>
+        <v>409</v>
       </c>
       <c r="L565" s="8" t="s">
         <v>47</v>
@@ -28791,7 +28791,7 @@
         <v>46</v>
       </c>
       <c r="K566" s="7">
-        <v>369</v>
+        <v>51</v>
       </c>
       <c r="L566" s="8" t="s">
         <v>47</v>
@@ -28829,7 +28829,7 @@
         <v>52</v>
       </c>
       <c r="K567" s="9">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="L567" s="8" t="s">
         <v>47</v>
@@ -28867,7 +28867,7 @@
         <v>57</v>
       </c>
       <c r="K568" s="7">
-        <v>295</v>
+        <v>180</v>
       </c>
       <c r="L568" s="8" t="s">
         <v>47</v>
@@ -28905,7 +28905,7 @@
         <v>46</v>
       </c>
       <c r="K569" s="9">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="L569" s="8" t="s">
         <v>47</v>
@@ -28943,7 +28943,7 @@
         <v>52</v>
       </c>
       <c r="K570" s="7">
-        <v>102</v>
+        <v>423</v>
       </c>
       <c r="L570" s="8" t="s">
         <v>47</v>
@@ -28981,7 +28981,7 @@
         <v>57</v>
       </c>
       <c r="K571" s="9">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="L571" s="8" t="s">
         <v>47</v>
@@ -29019,7 +29019,7 @@
         <v>46</v>
       </c>
       <c r="K572" s="7">
-        <v>25</v>
+        <v>466</v>
       </c>
       <c r="L572" s="8" t="s">
         <v>47</v>
@@ -29057,7 +29057,7 @@
         <v>52</v>
       </c>
       <c r="K573" s="9">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="L573" s="8" t="s">
         <v>47</v>
@@ -29095,7 +29095,7 @@
         <v>57</v>
       </c>
       <c r="K574" s="7">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="L574" s="8" t="s">
         <v>47</v>
@@ -29133,7 +29133,7 @@
         <v>46</v>
       </c>
       <c r="K575" s="9">
-        <v>146</v>
+        <v>378</v>
       </c>
       <c r="L575" s="8" t="s">
         <v>47</v>
@@ -29171,7 +29171,7 @@
         <v>52</v>
       </c>
       <c r="K576" s="7">
-        <v>50</v>
+        <v>386</v>
       </c>
       <c r="L576" s="8" t="s">
         <v>47</v>
@@ -29209,7 +29209,7 @@
         <v>57</v>
       </c>
       <c r="K577" s="9">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="L577" s="8" t="s">
         <v>47</v>
@@ -29247,7 +29247,7 @@
         <v>46</v>
       </c>
       <c r="K578" s="7">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="L578" s="8" t="s">
         <v>47</v>
@@ -29285,7 +29285,7 @@
         <v>52</v>
       </c>
       <c r="K579" s="9">
-        <v>343</v>
+        <v>299</v>
       </c>
       <c r="L579" s="8" t="s">
         <v>47</v>
@@ -29323,7 +29323,7 @@
         <v>57</v>
       </c>
       <c r="K580" s="7">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="L580" s="8" t="s">
         <v>47</v>
@@ -29361,7 +29361,7 @@
         <v>46</v>
       </c>
       <c r="K581" s="9">
-        <v>454</v>
+        <v>36</v>
       </c>
       <c r="L581" s="8" t="s">
         <v>47</v>
@@ -29399,7 +29399,7 @@
         <v>52</v>
       </c>
       <c r="K582" s="7">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="L582" s="8" t="s">
         <v>47</v>
@@ -29437,7 +29437,7 @@
         <v>57</v>
       </c>
       <c r="K583" s="9">
-        <v>145</v>
+        <v>413</v>
       </c>
       <c r="L583" s="8" t="s">
         <v>47</v>
@@ -29475,7 +29475,7 @@
         <v>46</v>
       </c>
       <c r="K584" s="7">
-        <v>58</v>
+        <v>439</v>
       </c>
       <c r="L584" s="8" t="s">
         <v>47</v>
@@ -29513,7 +29513,7 @@
         <v>52</v>
       </c>
       <c r="K585" s="9">
-        <v>159</v>
+        <v>346</v>
       </c>
       <c r="L585" s="8" t="s">
         <v>47</v>
@@ -29551,7 +29551,7 @@
         <v>57</v>
       </c>
       <c r="K586" s="7">
-        <v>303</v>
+        <v>42</v>
       </c>
       <c r="L586" s="8" t="s">
         <v>47</v>
@@ -29589,7 +29589,7 @@
         <v>46</v>
       </c>
       <c r="K587" s="9">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="L587" s="8" t="s">
         <v>47</v>
@@ -29627,7 +29627,7 @@
         <v>52</v>
       </c>
       <c r="K588" s="7">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="L588" s="8" t="s">
         <v>47</v>
@@ -29665,7 +29665,7 @@
         <v>57</v>
       </c>
       <c r="K589" s="9">
-        <v>244</v>
+        <v>183</v>
       </c>
       <c r="L589" s="8" t="s">
         <v>47</v>
@@ -29703,7 +29703,7 @@
         <v>46</v>
       </c>
       <c r="K590" s="7">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="L590" s="8" t="s">
         <v>47</v>
@@ -29741,7 +29741,7 @@
         <v>52</v>
       </c>
       <c r="K591" s="9">
-        <v>212</v>
+        <v>113</v>
       </c>
       <c r="L591" s="8" t="s">
         <v>47</v>
@@ -29779,7 +29779,7 @@
         <v>57</v>
       </c>
       <c r="K592" s="7">
-        <v>329</v>
+        <v>427</v>
       </c>
       <c r="L592" s="8" t="s">
         <v>47</v>
@@ -29817,7 +29817,7 @@
         <v>46</v>
       </c>
       <c r="K593" s="9">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="L593" s="10" t="s">
         <v>162</v>
@@ -29855,7 +29855,7 @@
         <v>52</v>
       </c>
       <c r="K594" s="7">
-        <v>378</v>
+        <v>225</v>
       </c>
       <c r="L594" s="8" t="s">
         <v>47</v>
@@ -29893,7 +29893,7 @@
         <v>57</v>
       </c>
       <c r="K595" s="9">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L595" s="8" t="s">
         <v>47</v>
@@ -29931,7 +29931,7 @@
         <v>46</v>
       </c>
       <c r="K596" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="L596" s="8" t="s">
         <v>47</v>
@@ -29969,7 +29969,7 @@
         <v>52</v>
       </c>
       <c r="K597" s="9">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="L597" s="8" t="s">
         <v>47</v>
@@ -30007,7 +30007,7 @@
         <v>57</v>
       </c>
       <c r="K598" s="7">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L598" s="8" t="s">
         <v>47</v>
@@ -30045,7 +30045,7 @@
         <v>46</v>
       </c>
       <c r="K599" s="9">
-        <v>460</v>
+        <v>267</v>
       </c>
       <c r="L599" s="8" t="s">
         <v>47</v>
@@ -30083,7 +30083,7 @@
         <v>52</v>
       </c>
       <c r="K600" s="7">
-        <v>219</v>
+        <v>65</v>
       </c>
       <c r="L600" s="8" t="s">
         <v>47</v>
@@ -30121,7 +30121,7 @@
         <v>57</v>
       </c>
       <c r="K601" s="9">
-        <v>412</v>
+        <v>277</v>
       </c>
       <c r="L601" s="8" t="s">
         <v>47</v>
@@ -30159,7 +30159,7 @@
         <v>46</v>
       </c>
       <c r="K602" s="7">
-        <v>411</v>
+        <v>111</v>
       </c>
       <c r="L602" s="8" t="s">
         <v>47</v>
@@ -30197,7 +30197,7 @@
         <v>52</v>
       </c>
       <c r="K603" s="9">
-        <v>113</v>
+        <v>329</v>
       </c>
       <c r="L603" s="8" t="s">
         <v>47</v>
@@ -30235,7 +30235,7 @@
         <v>57</v>
       </c>
       <c r="K604" s="7">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="L604" s="11" t="s">
         <v>253</v>
@@ -30273,7 +30273,7 @@
         <v>46</v>
       </c>
       <c r="K605" s="9">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="L605" s="8" t="s">
         <v>47</v>
@@ -30311,7 +30311,7 @@
         <v>52</v>
       </c>
       <c r="K606" s="7">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L606" s="8" t="s">
         <v>47</v>
@@ -30349,7 +30349,7 @@
         <v>57</v>
       </c>
       <c r="K607" s="9">
-        <v>269</v>
+        <v>206</v>
       </c>
       <c r="L607" s="8" t="s">
         <v>47</v>
@@ -30387,7 +30387,7 @@
         <v>46</v>
       </c>
       <c r="K608" s="7">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="L608" s="8" t="s">
         <v>47</v>
@@ -30425,7 +30425,7 @@
         <v>52</v>
       </c>
       <c r="K609" s="9">
-        <v>331</v>
+        <v>101</v>
       </c>
       <c r="L609" s="8" t="s">
         <v>47</v>
@@ -30463,7 +30463,7 @@
         <v>57</v>
       </c>
       <c r="K610" s="7">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="L610" s="8" t="s">
         <v>47</v>
@@ -30501,7 +30501,7 @@
         <v>46</v>
       </c>
       <c r="K611" s="9">
-        <v>414</v>
+        <v>299</v>
       </c>
       <c r="L611" s="8" t="s">
         <v>47</v>
@@ -30539,7 +30539,7 @@
         <v>52</v>
       </c>
       <c r="K612" s="7">
-        <v>457</v>
+        <v>61</v>
       </c>
       <c r="L612" s="8" t="s">
         <v>47</v>
@@ -30577,7 +30577,7 @@
         <v>57</v>
       </c>
       <c r="K613" s="9">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="L613" s="8" t="s">
         <v>47</v>
@@ -30615,7 +30615,7 @@
         <v>46</v>
       </c>
       <c r="K614" s="7">
-        <v>93</v>
+        <v>277</v>
       </c>
       <c r="L614" s="8" t="s">
         <v>47</v>
@@ -30653,7 +30653,7 @@
         <v>52</v>
       </c>
       <c r="K615" s="9">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="L615" s="8" t="s">
         <v>47</v>
@@ -30691,7 +30691,7 @@
         <v>57</v>
       </c>
       <c r="K616" s="7">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L616" s="8" t="s">
         <v>47</v>
@@ -30729,7 +30729,7 @@
         <v>46</v>
       </c>
       <c r="K617" s="9">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="L617" s="8" t="s">
         <v>47</v>
@@ -30767,7 +30767,7 @@
         <v>52</v>
       </c>
       <c r="K618" s="7">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="L618" s="8" t="s">
         <v>47</v>
@@ -30805,7 +30805,7 @@
         <v>57</v>
       </c>
       <c r="K619" s="9">
-        <v>112</v>
+        <v>462</v>
       </c>
       <c r="L619" s="8" t="s">
         <v>47</v>
@@ -30843,7 +30843,7 @@
         <v>46</v>
       </c>
       <c r="K620" s="7">
-        <v>241</v>
+        <v>412</v>
       </c>
       <c r="L620" s="8" t="s">
         <v>47</v>
@@ -30881,7 +30881,7 @@
         <v>52</v>
       </c>
       <c r="K621" s="9">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="L621" s="8" t="s">
         <v>47</v>
@@ -30919,7 +30919,7 @@
         <v>57</v>
       </c>
       <c r="K622" s="7">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="L622" s="8" t="s">
         <v>47</v>
@@ -30957,7 +30957,7 @@
         <v>46</v>
       </c>
       <c r="K623" s="9">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="L623" s="8" t="s">
         <v>47</v>
@@ -30995,7 +30995,7 @@
         <v>52</v>
       </c>
       <c r="K624" s="7">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="L624" s="8" t="s">
         <v>47</v>
@@ -31033,7 +31033,7 @@
         <v>57</v>
       </c>
       <c r="K625" s="9">
-        <v>115</v>
+        <v>199</v>
       </c>
       <c r="L625" s="8" t="s">
         <v>47</v>
@@ -31071,7 +31071,7 @@
         <v>46</v>
       </c>
       <c r="K626" s="7">
-        <v>392</v>
+        <v>193</v>
       </c>
       <c r="L626" s="8" t="s">
         <v>47</v>
@@ -31109,7 +31109,7 @@
         <v>52</v>
       </c>
       <c r="K627" s="9">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L627" s="8" t="s">
         <v>47</v>
@@ -31147,7 +31147,7 @@
         <v>57</v>
       </c>
       <c r="K628" s="7">
-        <v>338</v>
+        <v>460</v>
       </c>
       <c r="L628" s="8" t="s">
         <v>47</v>
@@ -31185,7 +31185,7 @@
         <v>46</v>
       </c>
       <c r="K629" s="9">
-        <v>157</v>
+        <v>58</v>
       </c>
       <c r="L629" s="8" t="s">
         <v>47</v>
@@ -31223,7 +31223,7 @@
         <v>52</v>
       </c>
       <c r="K630" s="7">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="L630" s="10" t="s">
         <v>162</v>
@@ -31261,7 +31261,7 @@
         <v>57</v>
       </c>
       <c r="K631" s="9">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="L631" s="8" t="s">
         <v>47</v>
@@ -31299,7 +31299,7 @@
         <v>46</v>
       </c>
       <c r="K632" s="7">
-        <v>40</v>
+        <v>393</v>
       </c>
       <c r="L632" s="8" t="s">
         <v>47</v>
@@ -31375,7 +31375,7 @@
         <v>57</v>
       </c>
       <c r="K634" s="7">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="L634" s="8" t="s">
         <v>47</v>
@@ -31413,7 +31413,7 @@
         <v>46</v>
       </c>
       <c r="K635" s="9">
-        <v>443</v>
+        <v>132</v>
       </c>
       <c r="L635" s="8" t="s">
         <v>47</v>
@@ -31451,7 +31451,7 @@
         <v>52</v>
       </c>
       <c r="K636" s="7">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="L636" s="8" t="s">
         <v>47</v>
@@ -31489,7 +31489,7 @@
         <v>57</v>
       </c>
       <c r="K637" s="9">
-        <v>419</v>
+        <v>233</v>
       </c>
       <c r="L637" s="8" t="s">
         <v>47</v>
@@ -31527,7 +31527,7 @@
         <v>46</v>
       </c>
       <c r="K638" s="7">
-        <v>284</v>
+        <v>389</v>
       </c>
       <c r="L638" s="8" t="s">
         <v>47</v>
@@ -31565,7 +31565,7 @@
         <v>52</v>
       </c>
       <c r="K639" s="9">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="L639" s="8" t="s">
         <v>47</v>
@@ -31603,7 +31603,7 @@
         <v>57</v>
       </c>
       <c r="K640" s="7">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="L640" s="8" t="s">
         <v>47</v>
@@ -31641,7 +31641,7 @@
         <v>46</v>
       </c>
       <c r="K641" s="9">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="L641" s="8" t="s">
         <v>47</v>
@@ -31679,7 +31679,7 @@
         <v>52</v>
       </c>
       <c r="K642" s="7">
-        <v>420</v>
+        <v>208</v>
       </c>
       <c r="L642" s="8" t="s">
         <v>47</v>
@@ -31717,7 +31717,7 @@
         <v>57</v>
       </c>
       <c r="K643" s="9">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="L643" s="8" t="s">
         <v>47</v>
@@ -31755,7 +31755,7 @@
         <v>46</v>
       </c>
       <c r="K644" s="7">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="L644" s="8" t="s">
         <v>47</v>
@@ -31793,7 +31793,7 @@
         <v>52</v>
       </c>
       <c r="K645" s="9">
-        <v>435</v>
+        <v>140</v>
       </c>
       <c r="L645" s="8" t="s">
         <v>47</v>
@@ -31831,7 +31831,7 @@
         <v>57</v>
       </c>
       <c r="K646" s="7">
-        <v>304</v>
+        <v>68</v>
       </c>
       <c r="L646" s="8" t="s">
         <v>47</v>
@@ -31869,7 +31869,7 @@
         <v>46</v>
       </c>
       <c r="K647" s="9">
-        <v>163</v>
+        <v>361</v>
       </c>
       <c r="L647" s="8" t="s">
         <v>47</v>
@@ -31907,7 +31907,7 @@
         <v>52</v>
       </c>
       <c r="K648" s="7">
-        <v>333</v>
+        <v>68</v>
       </c>
       <c r="L648" s="8" t="s">
         <v>47</v>
@@ -31945,7 +31945,7 @@
         <v>57</v>
       </c>
       <c r="K649" s="9">
-        <v>363</v>
+        <v>460</v>
       </c>
       <c r="L649" s="8" t="s">
         <v>47</v>
@@ -31983,7 +31983,7 @@
         <v>46</v>
       </c>
       <c r="K650" s="7">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="L650" s="8" t="s">
         <v>47</v>
@@ -32021,7 +32021,7 @@
         <v>52</v>
       </c>
       <c r="K651" s="9">
-        <v>125</v>
+        <v>261</v>
       </c>
       <c r="L651" s="8" t="s">
         <v>47</v>
@@ -32059,7 +32059,7 @@
         <v>57</v>
       </c>
       <c r="K652" s="7">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="L652" s="8" t="s">
         <v>47</v>
@@ -32097,7 +32097,7 @@
         <v>46</v>
       </c>
       <c r="K653" s="9">
-        <v>193</v>
+        <v>88</v>
       </c>
       <c r="L653" s="8" t="s">
         <v>47</v>
@@ -32135,7 +32135,7 @@
         <v>52</v>
       </c>
       <c r="K654" s="7">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="L654" s="8" t="s">
         <v>47</v>
@@ -32173,7 +32173,7 @@
         <v>57</v>
       </c>
       <c r="K655" s="9">
-        <v>367</v>
+        <v>140</v>
       </c>
       <c r="L655" s="8" t="s">
         <v>47</v>
@@ -32211,7 +32211,7 @@
         <v>46</v>
       </c>
       <c r="K656" s="7">
-        <v>139</v>
+        <v>262</v>
       </c>
       <c r="L656" s="8" t="s">
         <v>47</v>
@@ -32249,7 +32249,7 @@
         <v>52</v>
       </c>
       <c r="K657" s="9">
-        <v>414</v>
+        <v>306</v>
       </c>
       <c r="L657" s="8" t="s">
         <v>47</v>
@@ -32287,7 +32287,7 @@
         <v>57</v>
       </c>
       <c r="K658" s="7">
-        <v>268</v>
+        <v>455</v>
       </c>
       <c r="L658" s="8" t="s">
         <v>47</v>
@@ -32325,7 +32325,7 @@
         <v>46</v>
       </c>
       <c r="K659" s="9">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="L659" s="8" t="s">
         <v>47</v>
@@ -32363,7 +32363,7 @@
         <v>52</v>
       </c>
       <c r="K660" s="7">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="L660" s="8" t="s">
         <v>47</v>
@@ -32401,7 +32401,7 @@
         <v>57</v>
       </c>
       <c r="K661" s="9">
-        <v>43</v>
+        <v>397</v>
       </c>
       <c r="L661" s="8" t="s">
         <v>47</v>
@@ -32439,7 +32439,7 @@
         <v>46</v>
       </c>
       <c r="K662" s="7">
-        <v>276</v>
+        <v>392</v>
       </c>
       <c r="L662" s="8" t="s">
         <v>47</v>
@@ -32477,7 +32477,7 @@
         <v>52</v>
       </c>
       <c r="K663" s="9">
-        <v>389</v>
+        <v>435</v>
       </c>
       <c r="L663" s="8" t="s">
         <v>47</v>
@@ -32515,7 +32515,7 @@
         <v>57</v>
       </c>
       <c r="K664" s="7">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="L664" s="8" t="s">
         <v>47</v>
@@ -32553,7 +32553,7 @@
         <v>46</v>
       </c>
       <c r="K665" s="9">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L665" s="8" t="s">
         <v>47</v>
@@ -32591,7 +32591,7 @@
         <v>52</v>
       </c>
       <c r="K666" s="7">
-        <v>237</v>
+        <v>403</v>
       </c>
       <c r="L666" s="8" t="s">
         <v>47</v>
@@ -32629,7 +32629,7 @@
         <v>57</v>
       </c>
       <c r="K667" s="9">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="L667" s="10" t="s">
         <v>162</v>
@@ -32667,7 +32667,7 @@
         <v>46</v>
       </c>
       <c r="K668" s="7">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="L668" s="8" t="s">
         <v>47</v>
@@ -32705,7 +32705,7 @@
         <v>52</v>
       </c>
       <c r="K669" s="9">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="L669" s="8" t="s">
         <v>47</v>
@@ -32743,7 +32743,7 @@
         <v>57</v>
       </c>
       <c r="K670" s="7">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="L670" s="8" t="s">
         <v>47</v>
@@ -32781,7 +32781,7 @@
         <v>46</v>
       </c>
       <c r="K671" s="9">
-        <v>189</v>
+        <v>288</v>
       </c>
       <c r="L671" s="11" t="s">
         <v>253</v>
@@ -32819,7 +32819,7 @@
         <v>52</v>
       </c>
       <c r="K672" s="7">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L672" s="8" t="s">
         <v>47</v>
@@ -32857,7 +32857,7 @@
         <v>57</v>
       </c>
       <c r="K673" s="9">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="L673" s="8" t="s">
         <v>47</v>
@@ -32895,7 +32895,7 @@
         <v>46</v>
       </c>
       <c r="K674" s="7">
-        <v>324</v>
+        <v>413</v>
       </c>
       <c r="L674" s="8" t="s">
         <v>47</v>
@@ -32933,7 +32933,7 @@
         <v>52</v>
       </c>
       <c r="K675" s="9">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="L675" s="8" t="s">
         <v>47</v>
@@ -32971,7 +32971,7 @@
         <v>57</v>
       </c>
       <c r="K676" s="7">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L676" s="8" t="s">
         <v>47</v>
@@ -33009,7 +33009,7 @@
         <v>46</v>
       </c>
       <c r="K677" s="9">
-        <v>131</v>
+        <v>429</v>
       </c>
       <c r="L677" s="8" t="s">
         <v>47</v>
@@ -33047,7 +33047,7 @@
         <v>52</v>
       </c>
       <c r="K678" s="7">
-        <v>376</v>
+        <v>430</v>
       </c>
       <c r="L678" s="8" t="s">
         <v>47</v>
@@ -33085,7 +33085,7 @@
         <v>57</v>
       </c>
       <c r="K679" s="9">
-        <v>59</v>
+        <v>404</v>
       </c>
       <c r="L679" s="8" t="s">
         <v>47</v>
@@ -33123,7 +33123,7 @@
         <v>46</v>
       </c>
       <c r="K680" s="7">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="L680" s="8" t="s">
         <v>47</v>
@@ -33161,7 +33161,7 @@
         <v>52</v>
       </c>
       <c r="K681" s="9">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="L681" s="8" t="s">
         <v>47</v>
@@ -33199,7 +33199,7 @@
         <v>57</v>
       </c>
       <c r="K682" s="7">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="L682" s="8" t="s">
         <v>47</v>
@@ -33237,7 +33237,7 @@
         <v>46</v>
       </c>
       <c r="K683" s="9">
-        <v>462</v>
+        <v>61</v>
       </c>
       <c r="L683" s="8" t="s">
         <v>47</v>
@@ -33275,7 +33275,7 @@
         <v>52</v>
       </c>
       <c r="K684" s="7">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="L684" s="8" t="s">
         <v>47</v>
@@ -33313,7 +33313,7 @@
         <v>57</v>
       </c>
       <c r="K685" s="9">
-        <v>291</v>
+        <v>43</v>
       </c>
       <c r="L685" s="8" t="s">
         <v>47</v>
@@ -33351,7 +33351,7 @@
         <v>46</v>
       </c>
       <c r="K686" s="7">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L686" s="8" t="s">
         <v>47</v>
@@ -33389,7 +33389,7 @@
         <v>52</v>
       </c>
       <c r="K687" s="9">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="L687" s="8" t="s">
         <v>47</v>
@@ -33427,7 +33427,7 @@
         <v>57</v>
       </c>
       <c r="K688" s="7">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="L688" s="8" t="s">
         <v>47</v>
@@ -33465,7 +33465,7 @@
         <v>46</v>
       </c>
       <c r="K689" s="9">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="L689" s="8" t="s">
         <v>47</v>
@@ -33503,7 +33503,7 @@
         <v>52</v>
       </c>
       <c r="K690" s="7">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="L690" s="8" t="s">
         <v>47</v>
@@ -33541,7 +33541,7 @@
         <v>57</v>
       </c>
       <c r="K691" s="9">
-        <v>134</v>
+        <v>292</v>
       </c>
       <c r="L691" s="8" t="s">
         <v>47</v>
@@ -33579,7 +33579,7 @@
         <v>46</v>
       </c>
       <c r="K692" s="7">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="L692" s="8" t="s">
         <v>47</v>
@@ -33617,7 +33617,7 @@
         <v>52</v>
       </c>
       <c r="K693" s="9">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="L693" s="8" t="s">
         <v>47</v>
@@ -33655,7 +33655,7 @@
         <v>57</v>
       </c>
       <c r="K694" s="7">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="L694" s="8" t="s">
         <v>47</v>
@@ -33693,7 +33693,7 @@
         <v>46</v>
       </c>
       <c r="K695" s="9">
-        <v>224</v>
+        <v>336</v>
       </c>
       <c r="L695" s="8" t="s">
         <v>47</v>
@@ -33731,7 +33731,7 @@
         <v>52</v>
       </c>
       <c r="K696" s="7">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="L696" s="8" t="s">
         <v>47</v>
@@ -33769,7 +33769,7 @@
         <v>57</v>
       </c>
       <c r="K697" s="9">
-        <v>445</v>
+        <v>366</v>
       </c>
       <c r="L697" s="8" t="s">
         <v>47</v>
@@ -33807,7 +33807,7 @@
         <v>46</v>
       </c>
       <c r="K698" s="7">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="L698" s="8" t="s">
         <v>47</v>
@@ -33845,7 +33845,7 @@
         <v>52</v>
       </c>
       <c r="K699" s="9">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="L699" s="8" t="s">
         <v>47</v>
@@ -33883,7 +33883,7 @@
         <v>57</v>
       </c>
       <c r="K700" s="7">
-        <v>463</v>
+        <v>150</v>
       </c>
       <c r="L700" s="8" t="s">
         <v>47</v>
@@ -33921,7 +33921,7 @@
         <v>46</v>
       </c>
       <c r="K701" s="9">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="L701" s="8" t="s">
         <v>47</v>
@@ -33959,7 +33959,7 @@
         <v>52</v>
       </c>
       <c r="K702" s="7">
-        <v>181</v>
+        <v>278</v>
       </c>
       <c r="L702" s="8" t="s">
         <v>47</v>
@@ -33997,7 +33997,7 @@
         <v>57</v>
       </c>
       <c r="K703" s="9">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="L703" s="8" t="s">
         <v>47</v>
@@ -34035,7 +34035,7 @@
         <v>46</v>
       </c>
       <c r="K704" s="7">
-        <v>430</v>
+        <v>141</v>
       </c>
       <c r="L704" s="10" t="s">
         <v>162</v>
@@ -34073,7 +34073,7 @@
         <v>52</v>
       </c>
       <c r="K705" s="9">
-        <v>229</v>
+        <v>428</v>
       </c>
       <c r="L705" s="8" t="s">
         <v>47</v>
@@ -34111,7 +34111,7 @@
         <v>57</v>
       </c>
       <c r="K706" s="7">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="L706" s="8" t="s">
         <v>47</v>
@@ -34149,7 +34149,7 @@
         <v>46</v>
       </c>
       <c r="K707" s="9">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="L707" s="8" t="s">
         <v>47</v>
@@ -34187,7 +34187,7 @@
         <v>52</v>
       </c>
       <c r="K708" s="7">
-        <v>433</v>
+        <v>271</v>
       </c>
       <c r="L708" s="8" t="s">
         <v>47</v>
@@ -34225,7 +34225,7 @@
         <v>57</v>
       </c>
       <c r="K709" s="9">
-        <v>97</v>
+        <v>348</v>
       </c>
       <c r="L709" s="8" t="s">
         <v>47</v>
@@ -34263,7 +34263,7 @@
         <v>46</v>
       </c>
       <c r="K710" s="7">
-        <v>339</v>
+        <v>279</v>
       </c>
       <c r="L710" s="8" t="s">
         <v>47</v>
@@ -34301,7 +34301,7 @@
         <v>52</v>
       </c>
       <c r="K711" s="9">
-        <v>38</v>
+        <v>469</v>
       </c>
       <c r="L711" s="8" t="s">
         <v>47</v>
@@ -34339,7 +34339,7 @@
         <v>57</v>
       </c>
       <c r="K712" s="7">
-        <v>173</v>
+        <v>244</v>
       </c>
       <c r="L712" s="8" t="s">
         <v>47</v>
@@ -34377,7 +34377,7 @@
         <v>46</v>
       </c>
       <c r="K713" s="9">
-        <v>415</v>
+        <v>379</v>
       </c>
       <c r="L713" s="8" t="s">
         <v>47</v>
@@ -34415,7 +34415,7 @@
         <v>52</v>
       </c>
       <c r="K714" s="7">
-        <v>197</v>
+        <v>343</v>
       </c>
       <c r="L714" s="8" t="s">
         <v>47</v>
@@ -34453,7 +34453,7 @@
         <v>57</v>
       </c>
       <c r="K715" s="9">
-        <v>375</v>
+        <v>434</v>
       </c>
       <c r="L715" s="8" t="s">
         <v>47</v>
@@ -34491,7 +34491,7 @@
         <v>46</v>
       </c>
       <c r="K716" s="7">
-        <v>452</v>
+        <v>139</v>
       </c>
       <c r="L716" s="8" t="s">
         <v>47</v>
@@ -34529,7 +34529,7 @@
         <v>52</v>
       </c>
       <c r="K717" s="9">
-        <v>34</v>
+        <v>435</v>
       </c>
       <c r="L717" s="8" t="s">
         <v>47</v>
@@ -34567,7 +34567,7 @@
         <v>57</v>
       </c>
       <c r="K718" s="7">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="L718" s="8" t="s">
         <v>47</v>
@@ -34605,7 +34605,7 @@
         <v>46</v>
       </c>
       <c r="K719" s="9">
-        <v>77</v>
+        <v>394</v>
       </c>
       <c r="L719" s="8" t="s">
         <v>47</v>
@@ -34643,7 +34643,7 @@
         <v>52</v>
       </c>
       <c r="K720" s="7">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L720" s="8" t="s">
         <v>47</v>
@@ -34681,7 +34681,7 @@
         <v>57</v>
       </c>
       <c r="K721" s="9">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="L721" s="8" t="s">
         <v>47</v>
@@ -34719,7 +34719,7 @@
         <v>46</v>
       </c>
       <c r="K722" s="7">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="L722" s="8" t="s">
         <v>47</v>
@@ -34757,7 +34757,7 @@
         <v>52</v>
       </c>
       <c r="K723" s="9">
-        <v>259</v>
+        <v>207</v>
       </c>
       <c r="L723" s="8" t="s">
         <v>47</v>
@@ -34795,7 +34795,7 @@
         <v>57</v>
       </c>
       <c r="K724" s="7">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="L724" s="8" t="s">
         <v>47</v>
@@ -34833,7 +34833,7 @@
         <v>46</v>
       </c>
       <c r="K725" s="9">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="L725" s="8" t="s">
         <v>47</v>
@@ -34871,7 +34871,7 @@
         <v>52</v>
       </c>
       <c r="K726" s="7">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="L726" s="8" t="s">
         <v>47</v>
@@ -34909,7 +34909,7 @@
         <v>57</v>
       </c>
       <c r="K727" s="9">
-        <v>371</v>
+        <v>126</v>
       </c>
       <c r="L727" s="8" t="s">
         <v>47</v>
@@ -34947,7 +34947,7 @@
         <v>46</v>
       </c>
       <c r="K728" s="7">
-        <v>434</v>
+        <v>349</v>
       </c>
       <c r="L728" s="8" t="s">
         <v>47</v>
@@ -34985,7 +34985,7 @@
         <v>52</v>
       </c>
       <c r="K729" s="9">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="L729" s="8" t="s">
         <v>47</v>
@@ -35023,7 +35023,7 @@
         <v>57</v>
       </c>
       <c r="K730" s="7">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="L730" s="8" t="s">
         <v>47</v>
@@ -35061,7 +35061,7 @@
         <v>46</v>
       </c>
       <c r="K731" s="9">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="L731" s="8" t="s">
         <v>47</v>
@@ -35099,7 +35099,7 @@
         <v>52</v>
       </c>
       <c r="K732" s="7">
-        <v>275</v>
+        <v>441</v>
       </c>
       <c r="L732" s="8" t="s">
         <v>47</v>
@@ -35137,7 +35137,7 @@
         <v>57</v>
       </c>
       <c r="K733" s="9">
-        <v>343</v>
+        <v>169</v>
       </c>
       <c r="L733" s="8" t="s">
         <v>47</v>
@@ -35175,7 +35175,7 @@
         <v>46</v>
       </c>
       <c r="K734" s="7">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="L734" s="8" t="s">
         <v>47</v>
@@ -35213,7 +35213,7 @@
         <v>52</v>
       </c>
       <c r="K735" s="9">
-        <v>452</v>
+        <v>87</v>
       </c>
       <c r="L735" s="8" t="s">
         <v>47</v>
@@ -35251,7 +35251,7 @@
         <v>57</v>
       </c>
       <c r="K736" s="7">
-        <v>454</v>
+        <v>116</v>
       </c>
       <c r="L736" s="8" t="s">
         <v>47</v>
@@ -35289,7 +35289,7 @@
         <v>46</v>
       </c>
       <c r="K737" s="9">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="L737" s="8" t="s">
         <v>47</v>
@@ -35327,7 +35327,7 @@
         <v>52</v>
       </c>
       <c r="K738" s="7">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="L738" s="11" t="s">
         <v>253</v>
@@ -35365,7 +35365,7 @@
         <v>57</v>
       </c>
       <c r="K739" s="9">
-        <v>58</v>
+        <v>389</v>
       </c>
       <c r="L739" s="8" t="s">
         <v>47</v>
@@ -35403,7 +35403,7 @@
         <v>46</v>
       </c>
       <c r="K740" s="7">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="L740" s="8" t="s">
         <v>47</v>
@@ -35441,7 +35441,7 @@
         <v>52</v>
       </c>
       <c r="K741" s="9">
-        <v>71</v>
+        <v>444</v>
       </c>
       <c r="L741" s="10" t="s">
         <v>162</v>
@@ -35479,7 +35479,7 @@
         <v>57</v>
       </c>
       <c r="K742" s="7">
-        <v>243</v>
+        <v>379</v>
       </c>
       <c r="L742" s="8" t="s">
         <v>47</v>
@@ -35517,7 +35517,7 @@
         <v>46</v>
       </c>
       <c r="K743" s="9">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="L743" s="8" t="s">
         <v>47</v>
@@ -35555,7 +35555,7 @@
         <v>52</v>
       </c>
       <c r="K744" s="7">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="L744" s="8" t="s">
         <v>47</v>
@@ -35593,7 +35593,7 @@
         <v>57</v>
       </c>
       <c r="K745" s="9">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="L745" s="8" t="s">
         <v>47</v>
@@ -35631,7 +35631,7 @@
         <v>46</v>
       </c>
       <c r="K746" s="7">
-        <v>408</v>
+        <v>289</v>
       </c>
       <c r="L746" s="8" t="s">
         <v>47</v>
@@ -35669,7 +35669,7 @@
         <v>52</v>
       </c>
       <c r="K747" s="9">
-        <v>110</v>
+        <v>448</v>
       </c>
       <c r="L747" s="8" t="s">
         <v>47</v>
@@ -35707,7 +35707,7 @@
         <v>57</v>
       </c>
       <c r="K748" s="7">
-        <v>407</v>
+        <v>250</v>
       </c>
       <c r="L748" s="8" t="s">
         <v>47</v>
@@ -35745,7 +35745,7 @@
         <v>46</v>
       </c>
       <c r="K749" s="9">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="L749" s="8" t="s">
         <v>47</v>
@@ -35783,7 +35783,7 @@
         <v>52</v>
       </c>
       <c r="K750" s="7">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="L750" s="8" t="s">
         <v>47</v>
@@ -35821,7 +35821,7 @@
         <v>57</v>
       </c>
       <c r="K751" s="9">
-        <v>294</v>
+        <v>426</v>
       </c>
       <c r="L751" s="8" t="s">
         <v>47</v>
